--- a/back-end/mkd_works_service/works_init_sprav.xlsx
+++ b/back-end/mkd_works_service/works_init_sprav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Housing Company Services(HCS)\back-end\mkd_works_service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039EDCF6-E664-4C19-9C37-6B838F17D9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F20627D-D600-4758-AA61-3EF4A3CB9616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="888">
   <si>
     <r>
       <rPr>
@@ -769,15 +769,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="15"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Устранение повреждений стен</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <i/>
         <sz val="15"/>
         <rFont val="Times New Roman"/>
@@ -856,31 +847,6 @@
         <rFont val="Times New Roman"/>
       </rPr>
       <t>Дефектные ведомости. Приложение 6 Положения об организации и проведении реконструкции, ремонта и технического обслуживания зданий, объектов коммунального и социальнокультурного назначения, утвержденного приказом Госкомархитектуры от 23.11.1988 г. №312</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Hoci'iaiioiuiciiiic </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>'гешюзшц ты и звукоизоляции сгон</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>Восстановление гидроизоляции стен</t>
     </r>
   </si>
   <si>
@@ -8837,6 +8803,18 @@
   </si>
   <si>
     <t>29.1.</t>
+  </si>
+  <si>
+    <t>Устранение повреждений стен</t>
+  </si>
+  <si>
+    <t>Восстановление гидроизоляции стен</t>
+  </si>
+  <si>
+    <t>Восстановление теплозащиты и звукоизоляции стен</t>
+  </si>
+  <si>
+    <t>По мере необходимости</t>
   </si>
 </sst>
 </file>
@@ -11776,7 +11754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="254">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -12214,6 +12192,108 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -12223,13 +12303,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="87" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="115" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="116" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="118" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="119" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="120" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
@@ -12238,14 +12405,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="100" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="102" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="133" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -12253,278 +12417,101 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="134" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="137" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="150" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="154" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="155" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="185" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="206" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="207" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="185" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="203" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="204" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="182" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="154" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="155" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="136" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="137" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="150" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="139" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="118" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="119" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="120" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="87" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="124" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="114" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="115" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="116" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12854,21 +12841,21 @@
       <c r="A1" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="239" t="s">
+      <c r="B1" s="147" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="240"/>
-      <c r="D1" s="241"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="149"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="209" t="s">
+      <c r="B2" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="210"/>
+      <c r="C2" s="151"/>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
@@ -12877,18 +12864,18 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="249" t="s">
+      <c r="A3" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="197" t="s">
+      <c r="B3" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="198"/>
-      <c r="D3" s="199"/>
+      <c r="C3" s="155"/>
+      <c r="D3" s="156"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="250"/>
+      <c r="A4" s="153"/>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
@@ -12903,7 +12890,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="150"/>
+      <c r="A5" s="157"/>
       <c r="B5" s="1"/>
       <c r="C5" s="105" t="s">
         <v>15</v>
@@ -12912,7 +12899,7 @@
       <c r="E5" s="11"/>
     </row>
     <row r="6" spans="1:5" ht="101.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="151"/>
+      <c r="A6" s="158"/>
       <c r="B6" s="12" t="s">
         <v>12</v>
       </c>
@@ -12927,7 +12914,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="117" x14ac:dyDescent="0.3">
-      <c r="A7" s="151"/>
+      <c r="A7" s="158"/>
       <c r="B7" s="15" t="s">
         <v>13</v>
       </c>
@@ -12942,7 +12929,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="59.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="152"/>
+      <c r="A8" s="159"/>
       <c r="B8" s="15" t="s">
         <v>14</v>
       </c>
@@ -12957,9 +12944,9 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="150"/>
+      <c r="A9" s="157"/>
       <c r="B9" s="104" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>26</v>
@@ -12972,7 +12959,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="39" x14ac:dyDescent="0.3">
-      <c r="A10" s="151"/>
+      <c r="A10" s="158"/>
       <c r="B10" s="17" t="s">
         <v>22</v>
       </c>
@@ -12987,7 +12974,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="58.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="151"/>
+      <c r="A11" s="158"/>
       <c r="B11" s="15" t="s">
         <v>23</v>
       </c>
@@ -13002,7 +12989,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="97.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="151"/>
+      <c r="A12" s="158"/>
       <c r="B12" s="15" t="s">
         <v>24</v>
       </c>
@@ -13017,7 +13004,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="98.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="152"/>
+      <c r="A13" s="159"/>
       <c r="B13" s="15" t="s">
         <v>25</v>
       </c>
@@ -13050,21 +13037,21 @@
       <c r="A15" s="114" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="186" t="s">
+      <c r="B15" s="160" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="187"/>
-      <c r="D15" s="188"/>
+      <c r="C15" s="161"/>
+      <c r="D15" s="162"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A16" s="115" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="211" t="s">
+      <c r="B16" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="213"/>
+      <c r="C16" s="164"/>
       <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
@@ -13073,18 +13060,18 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="194" t="s">
+      <c r="A17" s="165" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="197" t="s">
+      <c r="B17" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="198"/>
-      <c r="D17" s="199"/>
+      <c r="C17" s="155"/>
+      <c r="D17" s="156"/>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="195"/>
+      <c r="A18" s="166"/>
       <c r="B18" s="4" t="s">
         <v>39</v>
       </c>
@@ -13099,7 +13086,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A19" s="195"/>
+      <c r="A19" s="166"/>
       <c r="B19" s="4" t="s">
         <v>40</v>
       </c>
@@ -13114,7 +13101,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="90" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="196"/>
+      <c r="A20" s="167"/>
       <c r="B20" s="4" t="s">
         <v>41</v>
       </c>
@@ -13129,7 +13116,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="150"/>
+      <c r="A21" s="157"/>
       <c r="B21" s="23" t="s">
         <v>47</v>
       </c>
@@ -13144,7 +13131,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="151"/>
+      <c r="A22" s="158"/>
       <c r="B22" s="23" t="s">
         <v>48</v>
       </c>
@@ -13159,7 +13146,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A23" s="151"/>
+      <c r="A23" s="158"/>
       <c r="B23" s="24" t="s">
         <v>49</v>
       </c>
@@ -13174,7 +13161,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="151"/>
+      <c r="A24" s="158"/>
       <c r="B24" s="24" t="s">
         <v>50</v>
       </c>
@@ -13189,7 +13176,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="151"/>
+      <c r="A25" s="158"/>
       <c r="B25" s="19" t="s">
         <v>51</v>
       </c>
@@ -13204,7 +13191,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A26" s="151"/>
+      <c r="A26" s="158"/>
       <c r="B26" s="4" t="s">
         <v>52</v>
       </c>
@@ -13219,7 +13206,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="152"/>
+      <c r="A27" s="159"/>
       <c r="B27" s="4" t="s">
         <v>53</v>
       </c>
@@ -13237,91 +13224,91 @@
       <c r="A28" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="242" t="s">
+      <c r="B28" s="168" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="248"/>
-      <c r="D28" s="243"/>
+      <c r="C28" s="169"/>
+      <c r="D28" s="170"/>
       <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:5" ht="117" x14ac:dyDescent="0.3">
       <c r="A29" s="117" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="244" t="s">
+      <c r="B29" s="171" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="245"/>
+      <c r="C29" s="172"/>
       <c r="D29" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="19.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="173" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="175" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="176"/>
+      <c r="D30" s="177"/>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" ht="273.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="174"/>
+      <c r="B31" s="251" t="s">
+        <v>884</v>
+      </c>
+      <c r="C31" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E31" s="14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="19.5" x14ac:dyDescent="0.2">
-      <c r="A30" s="224" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="226" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" s="227"/>
-      <c r="D30" s="228"/>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" ht="273.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="225"/>
-      <c r="B31" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
     <row r="32" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="150"/>
+      <c r="A32" s="157"/>
       <c r="B32" s="30" t="s">
-        <v>73</v>
+        <v>886</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>89</v>
+        <v>78</v>
+      </c>
+      <c r="D32" s="253" t="s">
+        <v>887</v>
       </c>
       <c r="E32" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A33" s="151"/>
-      <c r="B33" s="4" t="s">
-        <v>74</v>
+      <c r="A33" s="158"/>
+      <c r="B33" s="252" t="s">
+        <v>885</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A34" s="151"/>
+      <c r="A34" s="158"/>
       <c r="B34" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>9</v>
@@ -13331,12 +13318,12 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="151"/>
+      <c r="A35" s="158"/>
       <c r="B35" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C35" s="27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>9</v>
@@ -13346,12 +13333,12 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A36" s="151"/>
+      <c r="A36" s="158"/>
       <c r="B36" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>9</v>
@@ -13361,12 +13348,12 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="151"/>
+      <c r="A37" s="158"/>
       <c r="B37" s="23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D37" s="31" t="s">
         <v>9</v>
@@ -13376,12 +13363,12 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A38" s="151"/>
+      <c r="A38" s="158"/>
       <c r="B38" s="19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>9</v>
@@ -13391,12 +13378,12 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="152"/>
+      <c r="A39" s="159"/>
       <c r="B39" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>9</v>
@@ -13406,12 +13393,12 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="150"/>
+      <c r="A40" s="157"/>
       <c r="B40" s="19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>9</v>
@@ -13421,12 +13408,12 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A41" s="151"/>
+      <c r="A41" s="158"/>
       <c r="B41" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C41" s="27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>9</v>
@@ -13436,12 +13423,12 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="151"/>
+      <c r="A42" s="158"/>
       <c r="B42" s="19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>9</v>
@@ -13451,12 +13438,12 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="151"/>
+      <c r="A43" s="158"/>
       <c r="B43" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D43" s="31" t="s">
         <v>9</v>
@@ -13466,12 +13453,12 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A44" s="151"/>
+      <c r="A44" s="158"/>
       <c r="B44" s="19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D44" s="31" t="s">
         <v>9</v>
@@ -13481,12 +13468,12 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="151"/>
+      <c r="A45" s="158"/>
       <c r="B45" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>9</v>
@@ -13496,12 +13483,12 @@
       </c>
     </row>
     <row r="46" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A46" s="151"/>
+      <c r="A46" s="158"/>
       <c r="B46" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>9</v>
@@ -13511,12 +13498,12 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A47" s="151"/>
+      <c r="A47" s="158"/>
       <c r="B47" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>9</v>
@@ -13526,12 +13513,12 @@
       </c>
     </row>
     <row r="48" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="152"/>
+      <c r="A48" s="159"/>
       <c r="B48" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>9</v>
@@ -13543,25 +13530,25 @@
     <row r="49" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="178"/>
       <c r="B49" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="185"/>
+      <c r="A50" s="179"/>
       <c r="B50" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>9</v>
@@ -13571,12 +13558,12 @@
       </c>
     </row>
     <row r="51" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A51" s="185"/>
+      <c r="A51" s="179"/>
       <c r="B51" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>9</v>
@@ -13586,12 +13573,12 @@
       </c>
     </row>
     <row r="52" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A52" s="179"/>
+      <c r="A52" s="180"/>
       <c r="B52" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>9</v>
@@ -13602,57 +13589,57 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="118" t="s">
-        <v>110</v>
-      </c>
-      <c r="B53" s="147" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="148"/>
-      <c r="D53" s="149"/>
+        <v>107</v>
+      </c>
+      <c r="B53" s="181" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="182"/>
+      <c r="D53" s="183"/>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="112" t="s">
-        <v>111</v>
-      </c>
-      <c r="B54" s="209" t="s">
-        <v>117</v>
-      </c>
-      <c r="C54" s="210"/>
+        <v>108</v>
+      </c>
+      <c r="B54" s="150" t="s">
+        <v>114</v>
+      </c>
+      <c r="C54" s="151"/>
       <c r="D54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="113"/>
-      <c r="B55" s="209" t="s">
-        <v>125</v>
-      </c>
-      <c r="C55" s="210"/>
+      <c r="B55" s="150" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" s="151"/>
       <c r="D55" s="18"/>
       <c r="E55" s="33"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="194" t="s">
+      <c r="A56" s="165" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="184" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="185"/>
+      <c r="D56" s="186"/>
+      <c r="E56" s="33"/>
+    </row>
+    <row r="57" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A57" s="166"/>
+      <c r="B57" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B56" s="162" t="s">
-        <v>126</v>
-      </c>
-      <c r="C56" s="208"/>
-      <c r="D56" s="163"/>
-      <c r="E56" s="33"/>
-    </row>
-    <row r="57" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A57" s="195"/>
-      <c r="B57" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="C57" s="20" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>9</v>
@@ -13662,12 +13649,12 @@
       </c>
     </row>
     <row r="58" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A58" s="195"/>
+      <c r="A58" s="166"/>
       <c r="B58" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>9</v>
@@ -13677,12 +13664,12 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="195"/>
+      <c r="A59" s="166"/>
       <c r="B59" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>9</v>
@@ -13692,12 +13679,12 @@
       </c>
     </row>
     <row r="60" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A60" s="195"/>
+      <c r="A60" s="166"/>
       <c r="B60" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>9</v>
@@ -13707,12 +13694,12 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A61" s="195"/>
+      <c r="A61" s="166"/>
       <c r="B61" s="19" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>9</v>
@@ -13722,12 +13709,12 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="195"/>
+      <c r="A62" s="166"/>
       <c r="B62" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C62" s="27" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>9</v>
@@ -13737,12 +13724,12 @@
       </c>
     </row>
     <row r="63" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="196"/>
+      <c r="A63" s="167"/>
       <c r="B63" s="23" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>9</v>
@@ -13754,10 +13741,10 @@
     <row r="64" spans="1:5" ht="117.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="178"/>
       <c r="B64" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D64" s="14" t="s">
         <v>19</v>
@@ -13767,12 +13754,12 @@
       </c>
     </row>
     <row r="65" spans="1:5" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A65" s="185"/>
+      <c r="A65" s="179"/>
       <c r="B65" s="17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C65" s="34" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D65" s="28" t="s">
         <v>19</v>
@@ -13782,12 +13769,12 @@
       </c>
     </row>
     <row r="66" spans="1:5" ht="58.5" x14ac:dyDescent="0.3">
-      <c r="A66" s="179"/>
+      <c r="A66" s="180"/>
       <c r="B66" s="17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D66" s="14" t="s">
         <v>19</v>
@@ -13798,48 +13785,48 @@
     </row>
     <row r="67" spans="1:5" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A67" s="119" t="s">
-        <v>141</v>
-      </c>
-      <c r="B67" s="219" t="s">
-        <v>147</v>
-      </c>
-      <c r="C67" s="220"/>
-      <c r="D67" s="221"/>
+        <v>138</v>
+      </c>
+      <c r="B67" s="187" t="s">
+        <v>144</v>
+      </c>
+      <c r="C67" s="188"/>
+      <c r="D67" s="189"/>
       <c r="E67" s="18"/>
     </row>
     <row r="68" spans="1:5" ht="117" x14ac:dyDescent="0.3">
       <c r="A68" s="117" t="s">
-        <v>142</v>
-      </c>
-      <c r="B68" s="244" t="s">
-        <v>148</v>
-      </c>
-      <c r="C68" s="245"/>
+        <v>139</v>
+      </c>
+      <c r="B68" s="171" t="s">
+        <v>145</v>
+      </c>
+      <c r="C68" s="172"/>
       <c r="D68" s="35" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="224" t="s">
-        <v>143</v>
-      </c>
-      <c r="B69" s="246" t="s">
+      <c r="A69" s="173" t="s">
+        <v>140</v>
+      </c>
+      <c r="B69" s="190" t="s">
         <v>66</v>
       </c>
-      <c r="C69" s="247"/>
+      <c r="C69" s="191"/>
       <c r="D69" s="36"/>
       <c r="E69" s="18"/>
     </row>
     <row r="70" spans="1:5" ht="137.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="225"/>
+      <c r="A70" s="174"/>
       <c r="B70" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D70" s="14" t="s">
         <v>19</v>
@@ -13849,12 +13836,12 @@
       </c>
     </row>
     <row r="71" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="150"/>
+      <c r="A71" s="157"/>
       <c r="B71" s="24" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>9</v>
@@ -13864,12 +13851,12 @@
       </c>
     </row>
     <row r="72" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A72" s="151"/>
+      <c r="A72" s="158"/>
       <c r="B72" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C72" s="27" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>9</v>
@@ -13879,12 +13866,12 @@
       </c>
     </row>
     <row r="73" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A73" s="151"/>
+      <c r="A73" s="158"/>
       <c r="B73" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C73" s="27" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>9</v>
@@ -13894,12 +13881,12 @@
       </c>
     </row>
     <row r="74" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A74" s="151"/>
+      <c r="A74" s="158"/>
       <c r="B74" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C74" s="27" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>9</v>
@@ -13909,12 +13896,12 @@
       </c>
     </row>
     <row r="75" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A75" s="151"/>
+      <c r="A75" s="158"/>
       <c r="B75" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C75" s="27" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>9</v>
@@ -13924,12 +13911,12 @@
       </c>
     </row>
     <row r="76" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A76" s="151"/>
+      <c r="A76" s="158"/>
       <c r="B76" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C76" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>9</v>
@@ -13939,12 +13926,12 @@
       </c>
     </row>
     <row r="77" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A77" s="151"/>
+      <c r="A77" s="158"/>
       <c r="B77" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C77" s="27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>9</v>
@@ -13954,12 +13941,12 @@
       </c>
     </row>
     <row r="78" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A78" s="151"/>
+      <c r="A78" s="158"/>
       <c r="B78" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C78" s="27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>9</v>
@@ -13969,12 +13956,12 @@
       </c>
     </row>
     <row r="79" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="152"/>
+      <c r="A79" s="159"/>
       <c r="B79" s="24" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>9</v>
@@ -13985,94 +13972,94 @@
     </row>
     <row r="80" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="116" t="s">
-        <v>174</v>
-      </c>
-      <c r="B80" s="242" t="s">
-        <v>176</v>
-      </c>
-      <c r="C80" s="243"/>
+        <v>171</v>
+      </c>
+      <c r="B80" s="168" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" s="170"/>
       <c r="D80" s="18"/>
     </row>
     <row r="81" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A81" s="117" t="s">
+        <v>172</v>
+      </c>
+      <c r="B81" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="C81" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="D81" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="B81" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="C81" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="115" t="s">
-        <v>179</v>
-      </c>
-      <c r="B82" s="217" t="s">
-        <v>180</v>
-      </c>
-      <c r="C82" s="218"/>
+        <v>176</v>
+      </c>
+      <c r="B82" s="192" t="s">
+        <v>177</v>
+      </c>
+      <c r="C82" s="193"/>
       <c r="D82" s="1"/>
       <c r="E82" s="18"/>
     </row>
     <row r="83" spans="1:5" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A83" s="178"/>
       <c r="B83" s="23" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A84" s="185"/>
+      <c r="A84" s="179"/>
       <c r="B84" s="19" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D84" s="31" t="s">
         <v>9</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A85" s="185"/>
+      <c r="A85" s="179"/>
       <c r="B85" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D85" s="38" t="s">
         <v>8</v>
       </c>
       <c r="E85" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="115.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="179"/>
+      <c r="A86" s="180"/>
       <c r="B86" s="23" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C86" s="39" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>11</v>
@@ -14082,18 +14069,18 @@
       <c r="A87" s="120"/>
       <c r="B87" s="1"/>
       <c r="C87" s="20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="40"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" s="150"/>
+      <c r="A88" s="157"/>
       <c r="B88" s="19" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>9</v>
@@ -14103,12 +14090,12 @@
       </c>
     </row>
     <row r="89" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A89" s="151"/>
+      <c r="A89" s="158"/>
       <c r="B89" s="23" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>9</v>
@@ -14118,12 +14105,12 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" s="151"/>
+      <c r="A90" s="158"/>
       <c r="B90" s="19" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C90" s="20" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D90" s="31" t="s">
         <v>9</v>
@@ -14133,12 +14120,12 @@
       </c>
     </row>
     <row r="91" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A91" s="151"/>
+      <c r="A91" s="158"/>
       <c r="B91" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C91" s="20" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>9</v>
@@ -14148,12 +14135,12 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" s="151"/>
+      <c r="A92" s="158"/>
       <c r="B92" s="19" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C92" s="27" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>9</v>
@@ -14163,12 +14150,12 @@
       </c>
     </row>
     <row r="93" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A93" s="151"/>
+      <c r="A93" s="158"/>
       <c r="B93" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C93" s="20" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>9</v>
@@ -14178,12 +14165,12 @@
       </c>
     </row>
     <row r="94" spans="1:5" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="152"/>
+      <c r="A94" s="159"/>
       <c r="B94" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C94" s="20" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>9</v>
@@ -14195,10 +14182,10 @@
     <row r="95" spans="1:5" ht="102.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A95" s="178"/>
       <c r="B95" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>9</v>
@@ -14208,12 +14195,12 @@
       </c>
     </row>
     <row r="96" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A96" s="185"/>
+      <c r="A96" s="179"/>
       <c r="B96" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C96" s="20" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>9</v>
@@ -14223,12 +14210,12 @@
       </c>
     </row>
     <row r="97" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A97" s="185"/>
+      <c r="A97" s="179"/>
       <c r="B97" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>9</v>
@@ -14238,12 +14225,12 @@
       </c>
     </row>
     <row r="98" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A98" s="185"/>
+      <c r="A98" s="179"/>
       <c r="B98" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C98" s="27" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>9</v>
@@ -14253,12 +14240,12 @@
       </c>
     </row>
     <row r="99" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A99" s="179"/>
+      <c r="A99" s="180"/>
       <c r="B99" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C99" s="20" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>9</v>
@@ -14269,57 +14256,57 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="114" t="s">
-        <v>209</v>
-      </c>
-      <c r="B100" s="186" t="s">
-        <v>215</v>
-      </c>
-      <c r="C100" s="187"/>
-      <c r="D100" s="188"/>
+        <v>206</v>
+      </c>
+      <c r="B100" s="160" t="s">
+        <v>212</v>
+      </c>
+      <c r="C100" s="161"/>
+      <c r="D100" s="162"/>
       <c r="E100" s="1"/>
     </row>
     <row r="101" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A101" s="121" t="s">
-        <v>876</v>
-      </c>
-      <c r="B101" s="192" t="s">
-        <v>216</v>
-      </c>
-      <c r="C101" s="193"/>
+        <v>873</v>
+      </c>
+      <c r="B101" s="194" t="s">
+        <v>213</v>
+      </c>
+      <c r="C101" s="195"/>
       <c r="D101" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E101" s="31" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="64.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A102" s="113"/>
-      <c r="B102" s="222" t="s">
-        <v>224</v>
-      </c>
-      <c r="C102" s="223"/>
+      <c r="B102" s="196" t="s">
+        <v>221</v>
+      </c>
+      <c r="C102" s="197"/>
       <c r="D102" s="36"/>
       <c r="E102" s="41"/>
     </row>
     <row r="103" spans="1:5" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A103" s="122" t="s">
-        <v>223</v>
-      </c>
-      <c r="B103" s="236" t="s">
-        <v>225</v>
-      </c>
-      <c r="C103" s="237"/>
-      <c r="D103" s="238"/>
+        <v>220</v>
+      </c>
+      <c r="B103" s="198" t="s">
+        <v>222</v>
+      </c>
+      <c r="C103" s="199"/>
+      <c r="D103" s="200"/>
       <c r="E103" s="41"/>
     </row>
     <row r="104" spans="1:5" ht="97.5" x14ac:dyDescent="0.3">
       <c r="A104" s="178"/>
       <c r="B104" s="12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D104" s="14" t="s">
         <v>19</v>
@@ -14329,12 +14316,12 @@
       </c>
     </row>
     <row r="105" spans="1:5" ht="117" x14ac:dyDescent="0.3">
-      <c r="A105" s="185"/>
+      <c r="A105" s="179"/>
       <c r="B105" s="15" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D105" s="14" t="s">
         <v>19</v>
@@ -14344,12 +14331,12 @@
       </c>
     </row>
     <row r="106" spans="1:5" ht="58.5" x14ac:dyDescent="0.3">
-      <c r="A106" s="185"/>
+      <c r="A106" s="179"/>
       <c r="B106" s="15" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D106" s="14" t="s">
         <v>19</v>
@@ -14359,12 +14346,12 @@
       </c>
     </row>
     <row r="107" spans="1:5" ht="39" x14ac:dyDescent="0.3">
-      <c r="A107" s="185"/>
+      <c r="A107" s="179"/>
       <c r="B107" s="12" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D107" s="28" t="s">
         <v>19</v>
@@ -14374,12 +14361,12 @@
       </c>
     </row>
     <row r="108" spans="1:5" ht="39" x14ac:dyDescent="0.3">
-      <c r="A108" s="185"/>
+      <c r="A108" s="179"/>
       <c r="B108" s="17" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D108" s="28" t="s">
         <v>19</v>
@@ -14389,12 +14376,12 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A109" s="185"/>
+      <c r="A109" s="179"/>
       <c r="B109" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D109" s="28" t="s">
         <v>19</v>
@@ -14404,12 +14391,12 @@
       </c>
     </row>
     <row r="110" spans="1:5" ht="97.5" x14ac:dyDescent="0.3">
-      <c r="A110" s="185"/>
+      <c r="A110" s="179"/>
       <c r="B110" s="15" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D110" s="14" t="s">
         <v>19</v>
@@ -14419,12 +14406,12 @@
       </c>
     </row>
     <row r="111" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="179"/>
+      <c r="A111" s="180"/>
       <c r="B111" s="12" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D111" s="28" t="s">
         <v>19</v>
@@ -14435,48 +14422,48 @@
     </row>
     <row r="112" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A112" s="114" t="s">
+        <v>239</v>
+      </c>
+      <c r="B112" s="201" t="s">
         <v>242</v>
       </c>
-      <c r="B112" s="155" t="s">
-        <v>245</v>
-      </c>
-      <c r="C112" s="156"/>
-      <c r="D112" s="157"/>
+      <c r="C112" s="202"/>
+      <c r="D112" s="203"/>
       <c r="E112" s="1"/>
     </row>
     <row r="113" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A113" s="115" t="s">
+        <v>240</v>
+      </c>
+      <c r="B113" s="150" t="s">
         <v>243</v>
       </c>
-      <c r="B113" s="209" t="s">
-        <v>246</v>
-      </c>
-      <c r="C113" s="210"/>
+      <c r="C113" s="151"/>
       <c r="D113" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" s="194" t="s">
+      <c r="A114" s="165" t="s">
+        <v>241</v>
+      </c>
+      <c r="B114" s="154" t="s">
+        <v>177</v>
+      </c>
+      <c r="C114" s="155"/>
+      <c r="D114" s="156"/>
+      <c r="E114" s="1"/>
+    </row>
+    <row r="115" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A115" s="166"/>
+      <c r="B115" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B114" s="197" t="s">
-        <v>180</v>
-      </c>
-      <c r="C114" s="198"/>
-      <c r="D114" s="199"/>
-      <c r="E114" s="1"/>
-    </row>
-    <row r="115" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A115" s="195"/>
-      <c r="B115" s="4" t="s">
-        <v>247</v>
-      </c>
       <c r="C115" s="20" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>9</v>
@@ -14486,12 +14473,12 @@
       </c>
     </row>
     <row r="116" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A116" s="195"/>
+      <c r="A116" s="166"/>
       <c r="B116" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>9</v>
@@ -14501,12 +14488,12 @@
       </c>
     </row>
     <row r="117" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A117" s="195"/>
+      <c r="A117" s="166"/>
       <c r="B117" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>9</v>
@@ -14516,12 +14503,12 @@
       </c>
     </row>
     <row r="118" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A118" s="195"/>
+      <c r="A118" s="166"/>
       <c r="B118" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>9</v>
@@ -14531,12 +14518,12 @@
       </c>
     </row>
     <row r="119" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A119" s="195"/>
+      <c r="A119" s="166"/>
       <c r="B119" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>9</v>
@@ -14546,27 +14533,27 @@
       </c>
     </row>
     <row r="120" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="196"/>
+      <c r="A120" s="167"/>
       <c r="B120" s="23" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C120" s="19" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D120" s="31" t="s">
         <v>9</v>
       </c>
       <c r="E120" s="31" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A121" s="178"/>
       <c r="B121" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C121" s="20" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>9</v>
@@ -14576,12 +14563,12 @@
       </c>
     </row>
     <row r="122" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A122" s="185"/>
+      <c r="A122" s="179"/>
       <c r="B122" s="23" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>9</v>
@@ -14591,12 +14578,12 @@
       </c>
     </row>
     <row r="123" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A123" s="185"/>
+      <c r="A123" s="179"/>
       <c r="B123" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C123" s="20" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>9</v>
@@ -14606,12 +14593,12 @@
       </c>
     </row>
     <row r="124" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A124" s="185"/>
+      <c r="A124" s="179"/>
       <c r="B124" s="19" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>9</v>
@@ -14621,12 +14608,12 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A125" s="179"/>
+      <c r="A125" s="180"/>
       <c r="B125" s="19" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C125" s="27" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>9</v>
@@ -14637,48 +14624,48 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="123" t="s">
-        <v>261</v>
-      </c>
-      <c r="B126" s="239" t="s">
-        <v>269</v>
-      </c>
-      <c r="C126" s="240"/>
-      <c r="D126" s="241"/>
+        <v>258</v>
+      </c>
+      <c r="B126" s="147" t="s">
+        <v>266</v>
+      </c>
+      <c r="C126" s="148"/>
+      <c r="D126" s="149"/>
       <c r="E126" s="1"/>
     </row>
     <row r="127" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A127" s="115" t="s">
-        <v>262</v>
-      </c>
-      <c r="B127" s="209" t="s">
-        <v>270</v>
-      </c>
-      <c r="C127" s="210"/>
+        <v>259</v>
+      </c>
+      <c r="B127" s="150" t="s">
+        <v>267</v>
+      </c>
+      <c r="C127" s="151"/>
       <c r="D127" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E127" s="31" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A128" s="194" t="s">
-        <v>263</v>
-      </c>
-      <c r="B128" s="234" t="s">
-        <v>271</v>
-      </c>
-      <c r="C128" s="235"/>
+      <c r="A128" s="165" t="s">
+        <v>260</v>
+      </c>
+      <c r="B128" s="204" t="s">
+        <v>268</v>
+      </c>
+      <c r="C128" s="205"/>
       <c r="D128" s="18"/>
       <c r="E128" s="1"/>
     </row>
     <row r="129" spans="1:5" ht="102.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="196"/>
+      <c r="A129" s="167"/>
       <c r="B129" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>9</v>
@@ -14691,18 +14678,18 @@
       <c r="A130" s="120"/>
       <c r="B130" s="1"/>
       <c r="C130" s="20" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D130" s="18"/>
       <c r="E130" s="42"/>
     </row>
     <row r="131" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A131" s="150"/>
+      <c r="A131" s="157"/>
       <c r="B131" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C131" s="20" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>9</v>
@@ -14712,12 +14699,12 @@
       </c>
     </row>
     <row r="132" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A132" s="151"/>
+      <c r="A132" s="158"/>
       <c r="B132" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C132" s="20" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>9</v>
@@ -14727,51 +14714,51 @@
       </c>
     </row>
     <row r="133" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A133" s="151"/>
+      <c r="A133" s="158"/>
       <c r="B133" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C133" s="43" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="90" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="152"/>
+      <c r="A134" s="159"/>
       <c r="B134" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C134" s="39" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="137.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="120"/>
       <c r="B135" s="1"/>
       <c r="C135" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D135" s="36"/>
       <c r="E135" s="41"/>
     </row>
     <row r="136" spans="1:5" ht="331.5" x14ac:dyDescent="0.3">
-      <c r="A136" s="150"/>
+      <c r="A136" s="157"/>
       <c r="B136" s="15" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C136" s="16" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D136" s="14" t="s">
         <v>19</v>
@@ -14781,12 +14768,12 @@
       </c>
     </row>
     <row r="137" spans="1:5" ht="78" x14ac:dyDescent="0.3">
-      <c r="A137" s="151"/>
+      <c r="A137" s="158"/>
       <c r="B137" s="15" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D137" s="14" t="s">
         <v>19</v>
@@ -14796,12 +14783,12 @@
       </c>
     </row>
     <row r="138" spans="1:5" ht="195.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="152"/>
+      <c r="A138" s="159"/>
       <c r="B138" s="15" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D138" s="14" t="s">
         <v>19</v>
@@ -14812,48 +14799,48 @@
     </row>
     <row r="139" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A139" s="124" t="s">
+        <v>295</v>
+      </c>
+      <c r="B139" s="201" t="s">
         <v>298</v>
       </c>
-      <c r="B139" s="155" t="s">
-        <v>301</v>
-      </c>
-      <c r="C139" s="156"/>
-      <c r="D139" s="157"/>
+      <c r="C139" s="202"/>
+      <c r="D139" s="203"/>
       <c r="E139" s="1"/>
     </row>
     <row r="140" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A140" s="125" t="s">
+        <v>296</v>
+      </c>
+      <c r="B140" s="206" t="s">
         <v>299</v>
-      </c>
-      <c r="B140" s="206" t="s">
-        <v>302</v>
       </c>
       <c r="C140" s="207"/>
       <c r="D140" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E140" s="31" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141" s="194" t="s">
+      <c r="A141" s="165" t="s">
+        <v>297</v>
+      </c>
+      <c r="B141" s="184" t="s">
+        <v>5</v>
+      </c>
+      <c r="C141" s="185"/>
+      <c r="D141" s="186"/>
+      <c r="E141" s="1"/>
+    </row>
+    <row r="142" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A142" s="166"/>
+      <c r="B142" s="23" t="s">
         <v>300</v>
       </c>
-      <c r="B141" s="162" t="s">
-        <v>5</v>
-      </c>
-      <c r="C141" s="208"/>
-      <c r="D141" s="163"/>
-      <c r="E141" s="1"/>
-    </row>
-    <row r="142" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A142" s="195"/>
-      <c r="B142" s="23" t="s">
-        <v>303</v>
-      </c>
       <c r="C142" s="20" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>9</v>
@@ -14863,90 +14850,90 @@
       </c>
     </row>
     <row r="143" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A143" s="195"/>
+      <c r="A143" s="166"/>
       <c r="B143" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C143" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="D143" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="D143" s="26" t="s">
+      <c r="E143" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="E143" s="3" t="s">
-        <v>314</v>
-      </c>
     </row>
     <row r="144" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A144" s="195"/>
+      <c r="A144" s="166"/>
       <c r="B144" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C144" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="D144" s="208" t="s">
         <v>309</v>
       </c>
-      <c r="D144" s="172" t="s">
+      <c r="E144" s="208" t="s">
         <v>312</v>
       </c>
-      <c r="E144" s="172" t="s">
-        <v>315</v>
-      </c>
     </row>
     <row r="145" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="196"/>
+      <c r="A145" s="167"/>
       <c r="B145" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C145" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="D145" s="174"/>
-      <c r="E145" s="174"/>
+        <v>307</v>
+      </c>
+      <c r="D145" s="209"/>
+      <c r="E145" s="209"/>
     </row>
     <row r="146" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A146" s="106" t="s">
-        <v>873</v>
-      </c>
-      <c r="B146" s="186" t="s">
-        <v>318</v>
-      </c>
-      <c r="C146" s="187"/>
-      <c r="D146" s="188"/>
+        <v>870</v>
+      </c>
+      <c r="B146" s="160" t="s">
+        <v>315</v>
+      </c>
+      <c r="C146" s="161"/>
+      <c r="D146" s="162"/>
       <c r="E146" s="1"/>
     </row>
     <row r="147" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A147" s="112" t="s">
+        <v>313</v>
+      </c>
+      <c r="B147" s="206" t="s">
         <v>316</v>
-      </c>
-      <c r="B147" s="206" t="s">
-        <v>319</v>
       </c>
       <c r="C147" s="207"/>
       <c r="D147" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E147" s="26" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148" s="231" t="s">
+      <c r="A148" s="210" t="s">
+        <v>314</v>
+      </c>
+      <c r="B148" s="154" t="s">
+        <v>177</v>
+      </c>
+      <c r="C148" s="155"/>
+      <c r="D148" s="156"/>
+      <c r="E148" s="1"/>
+    </row>
+    <row r="149" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A149" s="211"/>
+      <c r="B149" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B148" s="197" t="s">
-        <v>180</v>
-      </c>
-      <c r="C148" s="198"/>
-      <c r="D148" s="199"/>
-      <c r="E148" s="1"/>
-    </row>
-    <row r="149" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A149" s="232"/>
-      <c r="B149" s="4" t="s">
-        <v>320</v>
-      </c>
       <c r="C149" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>9</v>
@@ -14956,12 +14943,12 @@
       </c>
     </row>
     <row r="150" spans="1:5" ht="141" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="233"/>
+      <c r="A150" s="212"/>
       <c r="B150" s="23" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>9</v>
@@ -14971,12 +14958,12 @@
       </c>
     </row>
     <row r="151" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="150"/>
+      <c r="A151" s="157"/>
       <c r="B151" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C151" s="25" t="s">
         <v>325</v>
-      </c>
-      <c r="C151" s="25" t="s">
-        <v>328</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>9</v>
@@ -14986,12 +14973,12 @@
       </c>
     </row>
     <row r="152" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A152" s="151"/>
+      <c r="A152" s="158"/>
       <c r="B152" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C152" s="25" t="s">
         <v>326</v>
-      </c>
-      <c r="C152" s="25" t="s">
-        <v>329</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>9</v>
@@ -15001,12 +14988,12 @@
       </c>
     </row>
     <row r="153" spans="1:5" ht="204.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="152"/>
+      <c r="A153" s="159"/>
       <c r="B153" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="C153" s="5" t="s">
         <v>327</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>330</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>9</v>
@@ -15017,48 +15004,48 @@
     </row>
     <row r="154" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A154" s="107" t="s">
-        <v>874</v>
-      </c>
-      <c r="B154" s="147" t="s">
-        <v>333</v>
-      </c>
-      <c r="C154" s="148"/>
-      <c r="D154" s="149"/>
+        <v>871</v>
+      </c>
+      <c r="B154" s="181" t="s">
+        <v>330</v>
+      </c>
+      <c r="C154" s="182"/>
+      <c r="D154" s="183"/>
       <c r="E154" s="1"/>
     </row>
     <row r="155" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A155" s="115" t="s">
+        <v>328</v>
+      </c>
+      <c r="B155" s="194" t="s">
         <v>331</v>
       </c>
-      <c r="B155" s="192" t="s">
-        <v>334</v>
-      </c>
-      <c r="C155" s="193"/>
+      <c r="C155" s="195"/>
       <c r="D155" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A156" s="194" t="s">
+      <c r="A156" s="165" t="s">
+        <v>329</v>
+      </c>
+      <c r="B156" s="154" t="s">
+        <v>177</v>
+      </c>
+      <c r="C156" s="155"/>
+      <c r="D156" s="156"/>
+      <c r="E156" s="1"/>
+    </row>
+    <row r="157" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A157" s="166"/>
+      <c r="B157" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B156" s="197" t="s">
-        <v>180</v>
-      </c>
-      <c r="C156" s="198"/>
-      <c r="D156" s="199"/>
-      <c r="E156" s="1"/>
-    </row>
-    <row r="157" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A157" s="195"/>
-      <c r="B157" s="4" t="s">
-        <v>335</v>
-      </c>
       <c r="C157" s="27" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>9</v>
@@ -15068,27 +15055,27 @@
       </c>
     </row>
     <row r="158" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A158" s="195"/>
+      <c r="A158" s="166"/>
       <c r="B158" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C158" s="27" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A159" s="195"/>
+      <c r="A159" s="166"/>
       <c r="B159" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C159" s="20" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>9</v>
@@ -15098,12 +15085,12 @@
       </c>
     </row>
     <row r="160" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A160" s="195"/>
+      <c r="A160" s="166"/>
       <c r="B160" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C160" s="20" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>9</v>
@@ -15113,12 +15100,12 @@
       </c>
     </row>
     <row r="161" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A161" s="196"/>
+      <c r="A161" s="167"/>
       <c r="B161" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C161" s="27" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>9</v>
@@ -15130,10 +15117,10 @@
     <row r="163" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A163" s="120"/>
       <c r="B163" s="23" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C163" s="48" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>9</v>
@@ -15144,48 +15131,48 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="125" t="s">
-        <v>348</v>
-      </c>
-      <c r="B164" s="147" t="s">
-        <v>352</v>
-      </c>
-      <c r="C164" s="148"/>
-      <c r="D164" s="149"/>
+        <v>345</v>
+      </c>
+      <c r="B164" s="181" t="s">
+        <v>349</v>
+      </c>
+      <c r="C164" s="182"/>
+      <c r="D164" s="183"/>
       <c r="E164" s="1"/>
     </row>
     <row r="165" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A165" s="115" t="s">
-        <v>349</v>
-      </c>
-      <c r="B165" s="192" t="s">
-        <v>353</v>
-      </c>
-      <c r="C165" s="193"/>
+        <v>346</v>
+      </c>
+      <c r="B165" s="194" t="s">
+        <v>350</v>
+      </c>
+      <c r="C165" s="195"/>
       <c r="D165" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E165" s="31" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A166" s="214" t="s">
-        <v>350</v>
-      </c>
-      <c r="B166" s="162" t="s">
-        <v>180</v>
-      </c>
-      <c r="C166" s="208"/>
-      <c r="D166" s="163"/>
+      <c r="A166" s="213" t="s">
+        <v>347</v>
+      </c>
+      <c r="B166" s="184" t="s">
+        <v>177</v>
+      </c>
+      <c r="C166" s="185"/>
+      <c r="D166" s="186"/>
       <c r="E166" s="1"/>
     </row>
     <row r="167" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A167" s="215"/>
+      <c r="A167" s="214"/>
       <c r="B167" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="C167" s="27" t="s">
         <v>354</v>
-      </c>
-      <c r="C167" s="27" t="s">
-        <v>357</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>9</v>
@@ -15195,12 +15182,12 @@
       </c>
     </row>
     <row r="168" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="216"/>
+      <c r="A168" s="215"/>
       <c r="B168" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C168" s="27" t="s">
         <v>355</v>
-      </c>
-      <c r="C168" s="27" t="s">
-        <v>358</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>9</v>
@@ -15210,27 +15197,27 @@
       </c>
     </row>
     <row r="169" spans="1:5" ht="90" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="150"/>
+      <c r="A169" s="157"/>
       <c r="B169" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C169" s="27" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E169" s="26" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A170" s="151"/>
+      <c r="A170" s="158"/>
       <c r="B170" s="23" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C170" s="20" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>9</v>
@@ -15240,92 +15227,92 @@
       </c>
     </row>
     <row r="171" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A171" s="151"/>
+      <c r="A171" s="158"/>
       <c r="B171" s="24" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C171" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="D171" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D171" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="E171" s="153" t="s">
-        <v>372</v>
+      <c r="E171" s="216" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="152"/>
+      <c r="A172" s="159"/>
       <c r="B172" s="4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C172" s="27" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="E172" s="154"/>
+        <v>367</v>
+      </c>
+      <c r="E172" s="217"/>
     </row>
     <row r="173" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A173" s="114" t="s">
+        <v>370</v>
+      </c>
+      <c r="B173" s="181" t="s">
         <v>373</v>
       </c>
-      <c r="B173" s="147" t="s">
-        <v>376</v>
-      </c>
-      <c r="C173" s="148"/>
-      <c r="D173" s="149"/>
+      <c r="C173" s="182"/>
+      <c r="D173" s="183"/>
       <c r="E173" s="1"/>
     </row>
     <row r="174" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A174" s="115" t="s">
+        <v>371</v>
+      </c>
+      <c r="B174" s="218" t="s">
         <v>374</v>
       </c>
-      <c r="B174" s="229" t="s">
-        <v>377</v>
-      </c>
-      <c r="C174" s="230"/>
+      <c r="C174" s="219"/>
       <c r="D174" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A175" s="194" t="s">
+      <c r="A175" s="165" t="s">
+        <v>372</v>
+      </c>
+      <c r="B175" s="184" t="s">
+        <v>177</v>
+      </c>
+      <c r="C175" s="185"/>
+      <c r="D175" s="186"/>
+      <c r="E175" s="1"/>
+    </row>
+    <row r="176" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A176" s="166"/>
+      <c r="B176" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="B175" s="162" t="s">
-        <v>180</v>
-      </c>
-      <c r="C175" s="208"/>
-      <c r="D175" s="163"/>
-      <c r="E175" s="1"/>
-    </row>
-    <row r="176" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A176" s="195"/>
-      <c r="B176" s="4" t="s">
-        <v>378</v>
-      </c>
       <c r="C176" s="49" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E176" s="31" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A177" s="195"/>
+      <c r="A177" s="166"/>
       <c r="B177" s="24" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D177" s="26" t="s">
         <v>9</v>
@@ -15335,12 +15322,12 @@
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A178" s="195"/>
+      <c r="A178" s="166"/>
       <c r="B178" s="24" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C178" s="51" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D178" s="26" t="s">
         <v>9</v>
@@ -15350,12 +15337,12 @@
       </c>
     </row>
     <row r="179" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="196"/>
+      <c r="A179" s="167"/>
       <c r="B179" s="23" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C179" s="25" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D179" s="26" t="s">
         <v>9</v>
@@ -15367,10 +15354,10 @@
     <row r="180" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A180" s="178"/>
       <c r="B180" s="4" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C180" s="25" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D180" s="3" t="s">
         <v>9</v>
@@ -15380,12 +15367,12 @@
       </c>
     </row>
     <row r="181" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A181" s="185"/>
+      <c r="A181" s="179"/>
       <c r="B181" s="4" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C181" s="25" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>9</v>
@@ -15395,12 +15382,12 @@
       </c>
     </row>
     <row r="182" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A182" s="185"/>
+      <c r="A182" s="179"/>
       <c r="B182" s="24" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D182" s="26" t="s">
         <v>9</v>
@@ -15410,12 +15397,12 @@
       </c>
     </row>
     <row r="183" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A183" s="179"/>
+      <c r="A183" s="180"/>
       <c r="B183" s="23" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C183" s="25" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D183" s="26" t="s">
         <v>9</v>
@@ -15427,10 +15414,10 @@
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="178"/>
       <c r="B184" s="52" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C184" s="25" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D184" s="26" t="s">
         <v>9</v>
@@ -15440,12 +15427,12 @@
       </c>
     </row>
     <row r="185" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A185" s="179"/>
+      <c r="A185" s="180"/>
       <c r="B185" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C185" s="25" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D185" s="3" t="s">
         <v>9</v>
@@ -15456,82 +15443,82 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="125" t="s">
-        <v>389</v>
-      </c>
-      <c r="B186" s="147" t="s">
-        <v>397</v>
-      </c>
-      <c r="C186" s="148"/>
-      <c r="D186" s="149"/>
+        <v>386</v>
+      </c>
+      <c r="B186" s="181" t="s">
+        <v>394</v>
+      </c>
+      <c r="C186" s="182"/>
+      <c r="D186" s="183"/>
       <c r="E186" s="1"/>
     </row>
     <row r="187" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A187" s="115" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B187" s="206" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C187" s="207"/>
       <c r="D187" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E187" s="26" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="213" t="s">
+        <v>403</v>
+      </c>
+      <c r="B188" s="192" t="s">
+        <v>404</v>
+      </c>
+      <c r="C188" s="193"/>
+      <c r="D188" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="E188" s="26" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A189" s="214"/>
+      <c r="B189" s="4" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="214" t="s">
+      <c r="C189" s="27" t="s">
+        <v>409</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E189" s="26" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A190" s="214"/>
+      <c r="B190" s="53" t="s">
         <v>406</v>
       </c>
-      <c r="B188" s="217" t="s">
-        <v>407</v>
-      </c>
-      <c r="C188" s="218"/>
-      <c r="D188" s="26" t="s">
-        <v>416</v>
-      </c>
-      <c r="E188" s="26" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A189" s="215"/>
-      <c r="B189" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="C189" s="27" t="s">
-        <v>412</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E189" s="26" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A190" s="215"/>
-      <c r="B190" s="53" t="s">
-        <v>409</v>
-      </c>
       <c r="C190" s="54" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E190" s="55" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A191" s="215"/>
+      <c r="A191" s="214"/>
       <c r="B191" s="23" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C191" s="25" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>9</v>
@@ -15541,12 +15528,12 @@
       </c>
     </row>
     <row r="192" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="216"/>
+      <c r="A192" s="215"/>
       <c r="B192" s="52" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C192" s="25" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D192" s="26" t="s">
         <v>9</v>
@@ -15557,93 +15544,93 @@
     </row>
     <row r="193" spans="1:5" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="119" t="s">
+        <v>418</v>
+      </c>
+      <c r="B193" s="187" t="s">
         <v>421</v>
       </c>
-      <c r="B193" s="219" t="s">
-        <v>424</v>
-      </c>
-      <c r="C193" s="220"/>
-      <c r="D193" s="221"/>
+      <c r="C193" s="188"/>
+      <c r="D193" s="189"/>
       <c r="E193" s="1"/>
     </row>
     <row r="194" spans="1:5" ht="292.5" x14ac:dyDescent="0.3">
       <c r="A194" s="117" t="s">
+        <v>419</v>
+      </c>
+      <c r="B194" s="196" t="s">
         <v>422</v>
       </c>
-      <c r="B194" s="222" t="s">
+      <c r="C194" s="197"/>
+      <c r="D194" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="C194" s="223"/>
-      <c r="D194" s="14" t="s">
+      <c r="E194" s="28" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="19.5" x14ac:dyDescent="0.2">
+      <c r="A195" s="173" t="s">
+        <v>420</v>
+      </c>
+      <c r="B195" s="175" t="s">
+        <v>222</v>
+      </c>
+      <c r="C195" s="176"/>
+      <c r="D195" s="177"/>
+      <c r="E195" s="1"/>
+    </row>
+    <row r="196" spans="1:5" ht="351.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="174"/>
+      <c r="B196" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="C196" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="D196" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="E196" s="14" t="s">
         <v>428</v>
       </c>
-      <c r="E194" s="28" t="s">
+    </row>
+    <row r="197" spans="1:5" ht="141" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="157"/>
+      <c r="B197" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C197" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A198" s="158"/>
+      <c r="B198" s="4" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" ht="19.5" x14ac:dyDescent="0.2">
-      <c r="A195" s="224" t="s">
-        <v>423</v>
-      </c>
-      <c r="B195" s="226" t="s">
-        <v>225</v>
-      </c>
-      <c r="C195" s="227"/>
-      <c r="D195" s="228"/>
-      <c r="E195" s="1"/>
-    </row>
-    <row r="196" spans="1:5" ht="351.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="225"/>
-      <c r="B196" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="C196" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="D196" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="E196" s="14" t="s">
+      <c r="C198" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="159"/>
+      <c r="B199" s="24" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" ht="141" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="150"/>
-      <c r="B197" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="C197" s="25" t="s">
-        <v>435</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A198" s="151"/>
-      <c r="B198" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="C198" s="25" t="s">
-        <v>436</v>
-      </c>
-      <c r="D198" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="E198" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="152"/>
-      <c r="B199" s="24" t="s">
+      <c r="C199" s="25" t="s">
         <v>434</v>
-      </c>
-      <c r="C199" s="25" t="s">
-        <v>437</v>
       </c>
       <c r="D199" s="26" t="s">
         <v>9</v>
@@ -15653,12 +15640,12 @@
       </c>
     </row>
     <row r="200" spans="1:5" ht="234.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A200" s="150"/>
+      <c r="A200" s="157"/>
       <c r="B200" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="C200" s="17" t="s">
         <v>441</v>
-      </c>
-      <c r="C200" s="17" t="s">
-        <v>444</v>
       </c>
       <c r="D200" s="14" t="s">
         <v>31</v>
@@ -15668,12 +15655,12 @@
       </c>
     </row>
     <row r="201" spans="1:5" ht="214.5" x14ac:dyDescent="0.3">
-      <c r="A201" s="151"/>
+      <c r="A201" s="158"/>
       <c r="B201" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="C201" s="17" t="s">
         <v>442</v>
-      </c>
-      <c r="C201" s="17" t="s">
-        <v>445</v>
       </c>
       <c r="D201" s="14" t="s">
         <v>19</v>
@@ -15683,12 +15670,12 @@
       </c>
     </row>
     <row r="202" spans="1:5" ht="312.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="152"/>
+      <c r="A202" s="159"/>
       <c r="B202" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="C202" s="17" t="s">
         <v>443</v>
-      </c>
-      <c r="C202" s="17" t="s">
-        <v>446</v>
       </c>
       <c r="D202" s="14" t="s">
         <v>19</v>
@@ -15701,7 +15688,7 @@
       <c r="A203" s="120"/>
       <c r="B203" s="1"/>
       <c r="C203" s="15" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D203" s="36"/>
       <c r="E203" s="41"/>
@@ -15709,10 +15696,10 @@
     <row r="204" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="126"/>
       <c r="B204" s="15" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C204" s="9" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D204" s="14" t="s">
         <v>19</v>
@@ -15725,7 +15712,7 @@
       <c r="A205" s="113"/>
       <c r="B205" s="1"/>
       <c r="C205" s="20" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D205" s="1"/>
       <c r="E205" s="18"/>
@@ -15733,10 +15720,10 @@
     <row r="206" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A206" s="178"/>
       <c r="B206" s="23" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C206" s="20" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>9</v>
@@ -15746,12 +15733,12 @@
       </c>
     </row>
     <row r="207" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A207" s="185"/>
+      <c r="A207" s="179"/>
       <c r="B207" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C207" s="20" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>9</v>
@@ -15761,12 +15748,12 @@
       </c>
     </row>
     <row r="208" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A208" s="179"/>
+      <c r="A208" s="180"/>
       <c r="B208" s="23" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C208" s="27" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>9</v>
@@ -15777,76 +15764,76 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="125" t="s">
-        <v>450</v>
-      </c>
-      <c r="B209" s="147" t="s">
-        <v>456</v>
-      </c>
-      <c r="C209" s="148"/>
-      <c r="D209" s="149"/>
+        <v>447</v>
+      </c>
+      <c r="B209" s="181" t="s">
+        <v>453</v>
+      </c>
+      <c r="C209" s="182"/>
+      <c r="D209" s="183"/>
       <c r="E209" s="18"/>
     </row>
     <row r="210" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A210" s="115" t="s">
-        <v>451</v>
-      </c>
-      <c r="B210" s="209" t="s">
-        <v>457</v>
-      </c>
-      <c r="C210" s="210"/>
+        <v>448</v>
+      </c>
+      <c r="B210" s="150" t="s">
+        <v>454</v>
+      </c>
+      <c r="C210" s="151"/>
       <c r="D210" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A211" s="220" t="s">
+        <v>449</v>
+      </c>
+      <c r="B211" s="163" t="s">
+        <v>455</v>
+      </c>
+      <c r="C211" s="222"/>
+      <c r="D211" s="164"/>
+      <c r="E211" s="18"/>
+    </row>
+    <row r="212" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="221"/>
+      <c r="B212" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C212" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="D212" s="223" t="s">
+        <v>463</v>
+      </c>
+      <c r="E212" s="224"/>
+    </row>
+    <row r="213" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="157"/>
+      <c r="B213" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="E210" s="3" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A211" s="158" t="s">
-        <v>452</v>
-      </c>
-      <c r="B211" s="211" t="s">
-        <v>458</v>
-      </c>
-      <c r="C211" s="212"/>
-      <c r="D211" s="213"/>
-      <c r="E211" s="18"/>
-    </row>
-    <row r="212" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="159"/>
-      <c r="B212" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="C212" s="20" t="s">
-        <v>464</v>
-      </c>
-      <c r="D212" s="190" t="s">
-        <v>466</v>
-      </c>
-      <c r="E212" s="191"/>
-    </row>
-    <row r="213" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="150"/>
-      <c r="B213" s="4" t="s">
-        <v>468</v>
-      </c>
       <c r="C213" s="27" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E213" s="31" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A214" s="151"/>
+      <c r="A214" s="158"/>
       <c r="B214" s="23" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C214" s="20" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D214" s="31" t="s">
         <v>9</v>
@@ -15856,12 +15843,12 @@
       </c>
     </row>
     <row r="215" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A215" s="151"/>
+      <c r="A215" s="158"/>
       <c r="B215" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C215" s="27" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>9</v>
@@ -15871,12 +15858,12 @@
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A216" s="151"/>
+      <c r="A216" s="158"/>
       <c r="B216" s="19" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C216" s="20" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D216" s="31" t="s">
         <v>9</v>
@@ -15886,12 +15873,12 @@
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A217" s="151"/>
+      <c r="A217" s="158"/>
       <c r="B217" s="19" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C217" s="20" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D217" s="31" t="s">
         <v>9</v>
@@ -15901,12 +15888,12 @@
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A218" s="151"/>
+      <c r="A218" s="158"/>
       <c r="B218" s="19" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C218" s="20" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D218" s="31" t="s">
         <v>9</v>
@@ -15916,12 +15903,12 @@
       </c>
     </row>
     <row r="219" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A219" s="151"/>
+      <c r="A219" s="158"/>
       <c r="B219" s="19" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C219" s="27" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>9</v>
@@ -15931,12 +15918,12 @@
       </c>
     </row>
     <row r="220" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A220" s="151"/>
+      <c r="A220" s="158"/>
       <c r="B220" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C220" s="20" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>9</v>
@@ -15946,12 +15933,12 @@
       </c>
     </row>
     <row r="221" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A221" s="151"/>
+      <c r="A221" s="158"/>
       <c r="B221" s="4" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C221" s="20" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D221" s="3" t="s">
         <v>9</v>
@@ -15961,27 +15948,27 @@
       </c>
     </row>
     <row r="222" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="152"/>
+      <c r="A222" s="159"/>
       <c r="B222" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C222" s="27" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="150"/>
+      <c r="A223" s="157"/>
       <c r="B223" s="23" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C223" s="20" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>9</v>
@@ -15991,12 +15978,12 @@
       </c>
     </row>
     <row r="224" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A224" s="151"/>
+      <c r="A224" s="158"/>
       <c r="B224" s="4" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C224" s="20" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>9</v>
@@ -16006,27 +15993,27 @@
       </c>
     </row>
     <row r="225" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A225" s="151"/>
+      <c r="A225" s="158"/>
       <c r="B225" s="23" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C225" s="27" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E225" s="31" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="179.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="152"/>
+      <c r="A226" s="159"/>
       <c r="B226" s="4" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C226" s="20" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>9</v>
@@ -16039,7 +16026,7 @@
       <c r="A227" s="120"/>
       <c r="B227" s="1"/>
       <c r="C227" s="9" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D227" s="36"/>
       <c r="E227" s="41"/>
@@ -16047,10 +16034,10 @@
     <row r="228" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="120"/>
       <c r="B228" s="15" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C228" s="9" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D228" s="14" t="s">
         <v>19</v>
@@ -16063,18 +16050,18 @@
       <c r="A229" s="120"/>
       <c r="B229" s="1"/>
       <c r="C229" s="20" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D229" s="18"/>
       <c r="E229" s="40"/>
     </row>
     <row r="230" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A230" s="150"/>
+      <c r="A230" s="157"/>
       <c r="B230" s="23" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C230" s="20" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>9</v>
@@ -16084,12 +16071,12 @@
       </c>
     </row>
     <row r="231" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A231" s="151"/>
+      <c r="A231" s="158"/>
       <c r="B231" s="23" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C231" s="20" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>9</v>
@@ -16099,25 +16086,25 @@
       </c>
     </row>
     <row r="232" spans="1:5" ht="141" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="152"/>
+      <c r="A232" s="159"/>
       <c r="B232" s="4" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C232" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="D232" s="190" t="s">
-        <v>509</v>
-      </c>
-      <c r="E232" s="191"/>
+        <v>505</v>
+      </c>
+      <c r="D232" s="223" t="s">
+        <v>506</v>
+      </c>
+      <c r="E232" s="224"/>
     </row>
     <row r="233" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A233" s="113"/>
       <c r="B233" s="24" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C233" s="25" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D233" s="26" t="s">
         <v>9</v>
@@ -16128,52 +16115,52 @@
     </row>
     <row r="234" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A234" s="127" t="s">
-        <v>510</v>
-      </c>
-      <c r="B234" s="203" t="s">
-        <v>512</v>
-      </c>
-      <c r="C234" s="204"/>
-      <c r="D234" s="205"/>
+        <v>507</v>
+      </c>
+      <c r="B234" s="225" t="s">
+        <v>509</v>
+      </c>
+      <c r="C234" s="226"/>
+      <c r="D234" s="227"/>
       <c r="E234" s="1"/>
     </row>
     <row r="235" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A235" s="128" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C235" s="27" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E235" s="172" t="s">
-        <v>531</v>
+        <v>527</v>
+      </c>
+      <c r="E235" s="208" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="236" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A236" s="129"/>
       <c r="B236" s="4" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C236" s="27" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E236" s="174"/>
+        <v>527</v>
+      </c>
+      <c r="E236" s="209"/>
     </row>
     <row r="237" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A237" s="128"/>
       <c r="B237" s="4" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C237" s="27" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D237" s="3" t="s">
         <v>9</v>
@@ -16185,64 +16172,64 @@
     <row r="238" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A238" s="128"/>
       <c r="B238" s="4" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C238" s="27" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E238" s="172" t="s">
-        <v>532</v>
+        <v>527</v>
+      </c>
+      <c r="E238" s="208" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A239" s="128"/>
       <c r="B239" s="4" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C239" s="27" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E239" s="173"/>
+        <v>527</v>
+      </c>
+      <c r="E239" s="228"/>
     </row>
     <row r="240" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A240" s="128"/>
       <c r="B240" s="4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C240" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="D240" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D240" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E240" s="173"/>
+      <c r="E240" s="228"/>
     </row>
     <row r="241" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A241" s="128"/>
       <c r="B241" s="4" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C241" s="27" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E241" s="174"/>
+        <v>527</v>
+      </c>
+      <c r="E241" s="209"/>
     </row>
     <row r="242" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A242" s="130"/>
       <c r="B242" s="4" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C242" s="20" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>9</v>
@@ -16253,48 +16240,48 @@
     </row>
     <row r="243" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A243" s="108" t="s">
-        <v>875</v>
-      </c>
-      <c r="B243" s="147" t="s">
-        <v>535</v>
-      </c>
-      <c r="C243" s="148"/>
-      <c r="D243" s="149"/>
+        <v>872</v>
+      </c>
+      <c r="B243" s="181" t="s">
+        <v>532</v>
+      </c>
+      <c r="C243" s="182"/>
+      <c r="D243" s="183"/>
       <c r="E243" s="18"/>
     </row>
     <row r="244" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A244" s="115" t="s">
+        <v>530</v>
+      </c>
+      <c r="B244" s="206" t="s">
         <v>533</v>
-      </c>
-      <c r="B244" s="206" t="s">
-        <v>536</v>
       </c>
       <c r="C244" s="207"/>
       <c r="D244" s="31" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E244" s="31" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="131" t="s">
+        <v>531</v>
+      </c>
+      <c r="B245" s="184" t="s">
         <v>534</v>
       </c>
-      <c r="B245" s="162" t="s">
-        <v>537</v>
-      </c>
-      <c r="C245" s="208"/>
-      <c r="D245" s="163"/>
+      <c r="C245" s="185"/>
+      <c r="D245" s="186"/>
       <c r="E245" s="18"/>
     </row>
     <row r="246" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A246" s="132"/>
       <c r="B246" s="4" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C246" s="20" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D246" s="3" t="s">
         <v>9</v>
@@ -16306,10 +16293,10 @@
     <row r="247" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A247" s="132"/>
       <c r="B247" s="4" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C247" s="20" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>9</v>
@@ -16321,10 +16308,10 @@
     <row r="248" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A248" s="132"/>
       <c r="B248" s="4" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C248" s="20" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>9</v>
@@ -16336,10 +16323,10 @@
     <row r="249" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A249" s="133"/>
       <c r="B249" s="19" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C249" s="20" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>9</v>
@@ -16349,12 +16336,12 @@
       </c>
     </row>
     <row r="250" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="150"/>
+      <c r="A250" s="157"/>
       <c r="B250" s="23" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C250" s="20" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>9</v>
@@ -16364,12 +16351,12 @@
       </c>
     </row>
     <row r="251" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A251" s="151"/>
+      <c r="A251" s="158"/>
       <c r="B251" s="23" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C251" s="20" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D251" s="3" t="s">
         <v>9</v>
@@ -16379,12 +16366,12 @@
       </c>
     </row>
     <row r="252" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A252" s="151"/>
+      <c r="A252" s="158"/>
       <c r="B252" s="4" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C252" s="20" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>9</v>
@@ -16394,12 +16381,12 @@
       </c>
     </row>
     <row r="253" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A253" s="151"/>
+      <c r="A253" s="158"/>
       <c r="B253" s="23" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C253" s="20" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D253" s="3" t="s">
         <v>9</v>
@@ -16409,12 +16396,12 @@
       </c>
     </row>
     <row r="254" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A254" s="151"/>
+      <c r="A254" s="158"/>
       <c r="B254" s="23" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C254" s="20" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>9</v>
@@ -16424,12 +16411,12 @@
       </c>
     </row>
     <row r="255" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A255" s="151"/>
+      <c r="A255" s="158"/>
       <c r="B255" s="23" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C255" s="57" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D255" s="45" t="s">
         <v>9</v>
@@ -16439,27 +16426,27 @@
       </c>
     </row>
     <row r="256" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A256" s="151"/>
+      <c r="A256" s="158"/>
       <c r="B256" s="58" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C256" s="59" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D256" s="56" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E256" s="46" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="257" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A257" s="151"/>
+      <c r="A257" s="158"/>
       <c r="B257" s="109" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="C257" s="20" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D257" s="46" t="s">
         <v>9</v>
@@ -16469,12 +16456,12 @@
       </c>
     </row>
     <row r="258" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A258" s="152"/>
+      <c r="A258" s="159"/>
       <c r="B258" s="23" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C258" s="20" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>9</v>
@@ -16486,23 +16473,23 @@
     <row r="259" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A259" s="134"/>
       <c r="B259" s="4" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C259" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="D259" s="190" t="s">
-        <v>581</v>
-      </c>
-      <c r="E259" s="191"/>
+        <v>570</v>
+      </c>
+      <c r="D259" s="223" t="s">
+        <v>578</v>
+      </c>
+      <c r="E259" s="224"/>
     </row>
     <row r="260" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A260" s="135"/>
       <c r="B260" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="C260" s="20" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>9</v>
@@ -16514,10 +16501,10 @@
     <row r="261" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A261" s="135"/>
       <c r="B261" s="23" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C261" s="20" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D261" s="3" t="s">
         <v>9</v>
@@ -16529,23 +16516,23 @@
     <row r="262" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A262" s="135"/>
       <c r="B262" s="4" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C262" s="20" t="s">
-        <v>576</v>
-      </c>
-      <c r="D262" s="190" t="s">
-        <v>582</v>
-      </c>
-      <c r="E262" s="191"/>
+        <v>573</v>
+      </c>
+      <c r="D262" s="223" t="s">
+        <v>579</v>
+      </c>
+      <c r="E262" s="224"/>
     </row>
     <row r="263" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A263" s="135"/>
       <c r="B263" s="23" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C263" s="20" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>9</v>
@@ -16557,10 +16544,10 @@
     <row r="264" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A264" s="135"/>
       <c r="B264" s="4" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C264" s="20" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>9</v>
@@ -16572,10 +16559,10 @@
     <row r="265" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A265" s="135"/>
       <c r="B265" s="4" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C265" s="20" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D265" s="3" t="s">
         <v>9</v>
@@ -16587,10 +16574,10 @@
     <row r="266" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A266" s="136"/>
       <c r="B266" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C266" s="20" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D266" s="3" t="s">
         <v>9</v>
@@ -16601,63 +16588,63 @@
     </row>
     <row r="267" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A267" s="114" t="s">
+        <v>580</v>
+      </c>
+      <c r="B267" s="201" t="s">
         <v>583</v>
       </c>
-      <c r="B267" s="155" t="s">
-        <v>586</v>
-      </c>
-      <c r="C267" s="156"/>
-      <c r="D267" s="157"/>
+      <c r="C267" s="202"/>
+      <c r="D267" s="203"/>
       <c r="E267" s="1"/>
     </row>
     <row r="268" spans="1:5" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A268" s="115" t="s">
+        <v>581</v>
+      </c>
+      <c r="B268" s="194" t="s">
         <v>584</v>
       </c>
-      <c r="B268" s="192" t="s">
+      <c r="C268" s="195"/>
+      <c r="D268" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E268" s="31" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A269" s="165" t="s">
+        <v>582</v>
+      </c>
+      <c r="B269" s="154" t="s">
+        <v>585</v>
+      </c>
+      <c r="C269" s="155"/>
+      <c r="D269" s="156"/>
+      <c r="E269" s="1"/>
+    </row>
+    <row r="270" spans="1:5" ht="102" x14ac:dyDescent="0.2">
+      <c r="A270" s="166"/>
+      <c r="B270" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="C270" s="20" t="s">
+        <v>590</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E270" s="31" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A271" s="166"/>
+      <c r="B271" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="C268" s="193"/>
-      <c r="D268" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="E268" s="31" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A269" s="194" t="s">
-        <v>585</v>
-      </c>
-      <c r="B269" s="197" t="s">
-        <v>588</v>
-      </c>
-      <c r="C269" s="198"/>
-      <c r="D269" s="199"/>
-      <c r="E269" s="1"/>
-    </row>
-    <row r="270" spans="1:5" ht="102" x14ac:dyDescent="0.2">
-      <c r="A270" s="195"/>
-      <c r="B270" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="C270" s="20" t="s">
-        <v>593</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E270" s="31" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A271" s="195"/>
-      <c r="B271" s="4" t="s">
-        <v>590</v>
-      </c>
       <c r="C271" s="20" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D271" s="3" t="s">
         <v>9</v>
@@ -16667,12 +16654,12 @@
       </c>
     </row>
     <row r="272" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A272" s="195"/>
+      <c r="A272" s="166"/>
       <c r="B272" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C272" s="20" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>9</v>
@@ -16682,66 +16669,66 @@
       </c>
     </row>
     <row r="273" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="196"/>
+      <c r="A273" s="167"/>
       <c r="B273" s="23" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C273" s="20" t="s">
-        <v>596</v>
-      </c>
-      <c r="D273" s="190" t="s">
-        <v>598</v>
-      </c>
-      <c r="E273" s="191"/>
+        <v>593</v>
+      </c>
+      <c r="D273" s="223" t="s">
+        <v>595</v>
+      </c>
+      <c r="E273" s="224"/>
     </row>
     <row r="274" spans="1:5" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A274" s="137" t="s">
-        <v>601</v>
-      </c>
-      <c r="B274" s="200" t="s">
-        <v>602</v>
-      </c>
-      <c r="C274" s="201"/>
-      <c r="D274" s="202"/>
+        <v>598</v>
+      </c>
+      <c r="B274" s="229" t="s">
+        <v>599</v>
+      </c>
+      <c r="C274" s="230"/>
+      <c r="D274" s="231"/>
       <c r="E274" s="1"/>
     </row>
     <row r="275" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A275" s="138" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B275" s="15" t="s">
+        <v>600</v>
+      </c>
+      <c r="C275" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="D275" s="35" t="s">
+        <v>602</v>
+      </c>
+      <c r="E275" s="14" t="s">
         <v>603</v>
-      </c>
-      <c r="C275" s="15" t="s">
-        <v>604</v>
-      </c>
-      <c r="D275" s="35" t="s">
-        <v>605</v>
-      </c>
-      <c r="E275" s="14" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="276" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A276" s="120"/>
       <c r="B276" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="C276" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="D276" s="35" t="s">
+        <v>606</v>
+      </c>
+      <c r="E276" s="14" t="s">
         <v>607</v>
-      </c>
-      <c r="C276" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="D276" s="35" t="s">
-        <v>609</v>
-      </c>
-      <c r="E276" s="14" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="277" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="120"/>
       <c r="B277" s="1"/>
       <c r="C277" s="9" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
@@ -16750,7 +16737,7 @@
       <c r="A278" s="120"/>
       <c r="B278" s="1"/>
       <c r="C278" s="9" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
@@ -16759,7 +16746,7 @@
       <c r="A279" s="120"/>
       <c r="B279" s="1"/>
       <c r="C279" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D279" s="60"/>
       <c r="E279" s="1"/>
@@ -16767,23 +16754,23 @@
     <row r="280" spans="1:5" ht="273.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A280" s="120"/>
       <c r="B280" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="C280" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="D280" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="E280" s="14" t="s">
         <v>613</v>
-      </c>
-      <c r="C280" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="D280" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E280" s="14" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="281" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="120"/>
       <c r="B281" s="1"/>
       <c r="C281" s="9" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
@@ -16792,7 +16779,7 @@
       <c r="A282" s="120"/>
       <c r="B282" s="1"/>
       <c r="C282" s="9" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="D282" s="42"/>
       <c r="E282" s="1"/>
@@ -16800,118 +16787,118 @@
     <row r="283" spans="1:5" ht="195.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A283" s="120"/>
       <c r="B283" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="D283" s="35" t="s">
         <v>618</v>
       </c>
-      <c r="C283" s="9" t="s">
+      <c r="E283" s="14" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="157"/>
+      <c r="B284" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="D283" s="35" t="s">
+      <c r="C284" s="20" t="s">
+        <v>622</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E284" s="31" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" ht="268.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A285" s="159"/>
+      <c r="B285" s="23" t="s">
         <v>621</v>
       </c>
-      <c r="E283" s="14" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A284" s="150"/>
-      <c r="B284" s="4" t="s">
+      <c r="C285" s="20" t="s">
         <v>623</v>
       </c>
-      <c r="C284" s="20" t="s">
-        <v>625</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="E284" s="31" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" ht="268.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="152"/>
-      <c r="B285" s="23" t="s">
-        <v>624</v>
-      </c>
-      <c r="C285" s="20" t="s">
+      <c r="D285" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E285" s="3" t="s">
         <v>626</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E285" s="3" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="286" spans="1:5" ht="102.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A286" s="120"/>
       <c r="B286" s="1"/>
       <c r="C286" s="20" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
     </row>
     <row r="287" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A287" s="150"/>
+      <c r="A287" s="157"/>
       <c r="B287" s="4" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C287" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A288" s="158"/>
+      <c r="B288" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="C288" s="27" t="s">
+        <v>632</v>
+      </c>
+      <c r="D288" s="31" t="s">
         <v>634</v>
       </c>
-      <c r="D287" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="E287" s="3" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A288" s="151"/>
-      <c r="B288" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="C288" s="27" t="s">
-        <v>635</v>
-      </c>
-      <c r="D288" s="31" t="s">
+      <c r="E288" s="4" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A289" s="159"/>
+      <c r="B289" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="C289" s="19" t="s">
+        <v>633</v>
+      </c>
+      <c r="D289" s="23" t="s">
+        <v>624</v>
+      </c>
+      <c r="E289" s="3" t="s">
         <v>637</v>
-      </c>
-      <c r="E288" s="4" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="152"/>
-      <c r="B289" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="C289" s="19" t="s">
-        <v>636</v>
-      </c>
-      <c r="D289" s="23" t="s">
-        <v>627</v>
-      </c>
-      <c r="E289" s="3" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="290" spans="1:5" ht="78.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A290" s="120"/>
       <c r="B290" s="1"/>
       <c r="C290" s="15" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D290" s="36"/>
       <c r="E290" s="1"/>
     </row>
     <row r="291" spans="1:5" ht="312" x14ac:dyDescent="0.3">
-      <c r="A291" s="150"/>
+      <c r="A291" s="157"/>
       <c r="B291" s="12" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C291" s="9" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D291" s="14" t="s">
         <v>19</v>
@@ -16921,1203 +16908,1203 @@
       </c>
     </row>
     <row r="292" spans="1:5" ht="117" x14ac:dyDescent="0.3">
-      <c r="A292" s="151"/>
+      <c r="A292" s="158"/>
       <c r="B292" s="15" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C292" s="13" t="s">
+        <v>643</v>
+      </c>
+      <c r="D292" s="35" t="s">
+        <v>645</v>
+      </c>
+      <c r="E292" s="28" t="s">
         <v>646</v>
       </c>
-      <c r="D292" s="35" t="s">
-        <v>648</v>
-      </c>
-      <c r="E292" s="28" t="s">
-        <v>649</v>
-      </c>
     </row>
     <row r="293" spans="1:5" ht="254.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A293" s="152"/>
+      <c r="A293" s="159"/>
       <c r="B293" s="15" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C293" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="D293" s="35" t="s">
+        <v>618</v>
+      </c>
+      <c r="E293" s="14" t="s">
         <v>647</v>
-      </c>
-      <c r="D293" s="35" t="s">
-        <v>621</v>
-      </c>
-      <c r="E293" s="14" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="294" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A294" s="127" t="s">
-        <v>651</v>
-      </c>
-      <c r="B294" s="186" t="s">
-        <v>652</v>
-      </c>
-      <c r="C294" s="187"/>
-      <c r="D294" s="188"/>
+        <v>648</v>
+      </c>
+      <c r="B294" s="160" t="s">
+        <v>649</v>
+      </c>
+      <c r="C294" s="161"/>
+      <c r="D294" s="162"/>
       <c r="E294" s="1"/>
     </row>
     <row r="295" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A295" s="139" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="B295" s="24" t="s">
-        <v>653</v>
-      </c>
-      <c r="C295" s="183" t="s">
-        <v>663</v>
+        <v>650</v>
+      </c>
+      <c r="C295" s="232" t="s">
+        <v>660</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="E295" s="172" t="s">
-        <v>675</v>
+        <v>665</v>
+      </c>
+      <c r="E295" s="208" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="296" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A296" s="128"/>
       <c r="B296" s="24" t="s">
-        <v>654</v>
-      </c>
-      <c r="C296" s="184"/>
+        <v>651</v>
+      </c>
+      <c r="C296" s="233"/>
       <c r="D296" s="1"/>
-      <c r="E296" s="173"/>
+      <c r="E296" s="228"/>
     </row>
     <row r="297" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A297" s="128"/>
       <c r="B297" s="61" t="s">
-        <v>655</v>
-      </c>
-      <c r="C297" s="184"/>
+        <v>652</v>
+      </c>
+      <c r="C297" s="233"/>
       <c r="D297" s="62" t="s">
-        <v>669</v>
-      </c>
-      <c r="E297" s="173"/>
+        <v>666</v>
+      </c>
+      <c r="E297" s="228"/>
     </row>
     <row r="298" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A298" s="128"/>
       <c r="B298" s="61" t="s">
-        <v>656</v>
-      </c>
-      <c r="C298" s="184"/>
+        <v>653</v>
+      </c>
+      <c r="C298" s="233"/>
       <c r="D298" s="62" t="s">
-        <v>669</v>
-      </c>
-      <c r="E298" s="173"/>
+        <v>666</v>
+      </c>
+      <c r="E298" s="228"/>
     </row>
     <row r="299" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A299" s="128"/>
       <c r="B299" s="61" t="s">
-        <v>657</v>
-      </c>
-      <c r="C299" s="184"/>
+        <v>654</v>
+      </c>
+      <c r="C299" s="233"/>
       <c r="D299" s="62" t="s">
-        <v>670</v>
-      </c>
-      <c r="E299" s="173"/>
+        <v>667</v>
+      </c>
+      <c r="E299" s="228"/>
     </row>
     <row r="300" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A300" s="128"/>
       <c r="B300" s="61" t="s">
-        <v>658</v>
-      </c>
-      <c r="C300" s="189"/>
+        <v>655</v>
+      </c>
+      <c r="C300" s="234"/>
       <c r="D300" s="62" t="s">
-        <v>671</v>
-      </c>
-      <c r="E300" s="174"/>
+        <v>668</v>
+      </c>
+      <c r="E300" s="209"/>
     </row>
     <row r="301" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A301" s="128"/>
       <c r="B301" s="23" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C301" s="27" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E301" s="31" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="302" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A302" s="128"/>
       <c r="B302" s="4" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C302" s="27" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D302" s="63" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E302" s="31" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="303" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A303" s="128"/>
       <c r="B303" s="4" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C303" s="27" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D303" s="19" t="s">
-        <v>674</v>
-      </c>
-      <c r="E303" s="164" t="s">
-        <v>678</v>
+        <v>671</v>
+      </c>
+      <c r="E303" s="235" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="304" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A304" s="130"/>
       <c r="B304" s="23" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C304" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E304" s="236"/>
+    </row>
+    <row r="305" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A305" s="157"/>
+      <c r="B305" s="24" t="s">
+        <v>676</v>
+      </c>
+      <c r="C305" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E305" s="235" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A306" s="158"/>
+      <c r="B306" s="23" t="s">
+        <v>677</v>
+      </c>
+      <c r="C306" s="27" t="s">
+        <v>688</v>
+      </c>
+      <c r="D306" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="D304" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="E304" s="166"/>
-    </row>
-    <row r="305" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A305" s="150"/>
-      <c r="B305" s="24" t="s">
+      <c r="E306" s="236"/>
+    </row>
+    <row r="307" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A307" s="158"/>
+      <c r="B307" s="19" t="s">
+        <v>678</v>
+      </c>
+      <c r="C307" s="27" t="s">
+        <v>689</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E307" s="208" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A308" s="158"/>
+      <c r="B308" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="C305" s="20" t="s">
+      <c r="C308" s="20" t="s">
         <v>690</v>
-      </c>
-      <c r="D305" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="E305" s="164" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A306" s="151"/>
-      <c r="B306" s="23" t="s">
-        <v>680</v>
-      </c>
-      <c r="C306" s="27" t="s">
-        <v>691</v>
-      </c>
-      <c r="D306" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="E306" s="166"/>
-    </row>
-    <row r="307" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A307" s="151"/>
-      <c r="B307" s="19" t="s">
-        <v>681</v>
-      </c>
-      <c r="C307" s="27" t="s">
-        <v>692</v>
-      </c>
-      <c r="D307" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E307" s="172" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A308" s="151"/>
-      <c r="B308" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="C308" s="20" t="s">
-        <v>693</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E308" s="174"/>
+      <c r="E308" s="209"/>
     </row>
     <row r="309" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A309" s="151"/>
+      <c r="A309" s="158"/>
       <c r="B309" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C309" s="27" t="s">
+        <v>691</v>
+      </c>
+      <c r="D309" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="E309" s="64" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A310" s="158"/>
+      <c r="B310" s="19" t="s">
+        <v>681</v>
+      </c>
+      <c r="C310" s="66" t="s">
+        <v>692</v>
+      </c>
+      <c r="D310" s="67" t="s">
+        <v>698</v>
+      </c>
+      <c r="E310" s="228" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A311" s="158"/>
+      <c r="B311" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="C311" s="68" t="s">
+        <v>693</v>
+      </c>
+      <c r="D311" s="47" t="s">
+        <v>699</v>
+      </c>
+      <c r="E311" s="228"/>
+    </row>
+    <row r="312" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A312" s="158"/>
+      <c r="B312" s="19" t="s">
         <v>683</v>
       </c>
-      <c r="C309" s="27" t="s">
+      <c r="C312" s="59" t="s">
         <v>694</v>
       </c>
-      <c r="D309" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="E309" s="64" t="s">
+      <c r="D312" s="22" t="s">
+        <v>527</v>
+      </c>
+      <c r="E312" s="228"/>
+    </row>
+    <row r="313" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A313" s="158"/>
+      <c r="B313" s="19" t="s">
+        <v>684</v>
+      </c>
+      <c r="C313" s="20" t="s">
+        <v>695</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E313" s="228"/>
+    </row>
+    <row r="314" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A314" s="158"/>
+      <c r="B314" s="19" t="s">
+        <v>685</v>
+      </c>
+      <c r="C314" s="20" t="s">
+        <v>696</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E314" s="228"/>
+    </row>
+    <row r="315" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A315" s="159"/>
+      <c r="B315" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="C315" s="27" t="s">
+        <v>697</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E315" s="209"/>
+    </row>
+    <row r="316" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A316" s="157"/>
+      <c r="B316" s="52" t="s">
+        <v>704</v>
+      </c>
+      <c r="C316" s="20" t="s">
+        <v>710</v>
+      </c>
+      <c r="D316" s="44" t="s">
+        <v>527</v>
+      </c>
+      <c r="E316" s="237"/>
+    </row>
+    <row r="317" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A317" s="158"/>
+      <c r="B317" s="19" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="310" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A310" s="151"/>
-      <c r="B310" s="19" t="s">
-        <v>684</v>
-      </c>
-      <c r="C310" s="66" t="s">
-        <v>695</v>
-      </c>
-      <c r="D310" s="67" t="s">
-        <v>701</v>
-      </c>
-      <c r="E310" s="173" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A311" s="151"/>
-      <c r="B311" s="19" t="s">
-        <v>685</v>
-      </c>
-      <c r="C311" s="68" t="s">
-        <v>696</v>
-      </c>
-      <c r="D311" s="47" t="s">
-        <v>702</v>
-      </c>
-      <c r="E311" s="173"/>
-    </row>
-    <row r="312" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A312" s="151"/>
-      <c r="B312" s="19" t="s">
-        <v>686</v>
-      </c>
-      <c r="C312" s="59" t="s">
-        <v>697</v>
-      </c>
-      <c r="D312" s="22" t="s">
-        <v>530</v>
-      </c>
-      <c r="E312" s="173"/>
-    </row>
-    <row r="313" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A313" s="151"/>
-      <c r="B313" s="19" t="s">
-        <v>687</v>
-      </c>
-      <c r="C313" s="20" t="s">
-        <v>698</v>
-      </c>
-      <c r="D313" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E313" s="173"/>
-    </row>
-    <row r="314" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A314" s="151"/>
-      <c r="B314" s="19" t="s">
-        <v>688</v>
-      </c>
-      <c r="C314" s="20" t="s">
-        <v>699</v>
-      </c>
-      <c r="D314" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E314" s="173"/>
-    </row>
-    <row r="315" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A315" s="152"/>
-      <c r="B315" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="C315" s="27" t="s">
-        <v>700</v>
-      </c>
-      <c r="D315" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E315" s="174"/>
-    </row>
-    <row r="316" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A316" s="150"/>
-      <c r="B316" s="52" t="s">
-        <v>707</v>
-      </c>
-      <c r="C316" s="20" t="s">
-        <v>713</v>
-      </c>
-      <c r="D316" s="44" t="s">
-        <v>530</v>
-      </c>
-      <c r="E316" s="180"/>
-    </row>
-    <row r="317" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A317" s="151"/>
-      <c r="B317" s="19" t="s">
-        <v>708</v>
-      </c>
       <c r="C317" s="20" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D317" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="E317" s="181"/>
+      <c r="E317" s="238"/>
     </row>
     <row r="318" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A318" s="151"/>
+      <c r="A318" s="158"/>
       <c r="B318" s="19" t="s">
+        <v>706</v>
+      </c>
+      <c r="C318" s="20" t="s">
+        <v>712</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E318" s="238"/>
+    </row>
+    <row r="319" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A319" s="158"/>
+      <c r="B319" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="C319" s="20" t="s">
+        <v>713</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E319" s="239"/>
+    </row>
+    <row r="320" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A320" s="158"/>
+      <c r="B320" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="C320" s="27" t="s">
+        <v>714</v>
+      </c>
+      <c r="D320" s="26" t="s">
+        <v>716</v>
+      </c>
+      <c r="E320" s="3" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="159"/>
+      <c r="B321" s="23" t="s">
         <v>709</v>
       </c>
-      <c r="C318" s="20" t="s">
+      <c r="C321" s="27" t="s">
         <v>715</v>
-      </c>
-      <c r="D318" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E318" s="181"/>
-    </row>
-    <row r="319" spans="1:5" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A319" s="151"/>
-      <c r="B319" s="4" t="s">
-        <v>710</v>
-      </c>
-      <c r="C319" s="20" t="s">
-        <v>716</v>
-      </c>
-      <c r="D319" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="E319" s="182"/>
-    </row>
-    <row r="320" spans="1:5" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A320" s="151"/>
-      <c r="B320" s="4" t="s">
-        <v>711</v>
-      </c>
-      <c r="C320" s="27" t="s">
-        <v>717</v>
-      </c>
-      <c r="D320" s="26" t="s">
-        <v>719</v>
-      </c>
-      <c r="E320" s="3" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A321" s="152"/>
-      <c r="B321" s="23" t="s">
-        <v>712</v>
-      </c>
-      <c r="C321" s="27" t="s">
-        <v>718</v>
       </c>
       <c r="D321" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E321" s="31" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="322" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A322" s="140" t="s">
-        <v>722</v>
-      </c>
-      <c r="B322" s="147" t="s">
-        <v>723</v>
-      </c>
-      <c r="C322" s="148"/>
-      <c r="D322" s="149"/>
+        <v>719</v>
+      </c>
+      <c r="B322" s="181" t="s">
+        <v>720</v>
+      </c>
+      <c r="C322" s="182"/>
+      <c r="D322" s="183"/>
       <c r="E322" s="1"/>
     </row>
     <row r="323" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A323" s="141" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C323" s="27" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D323" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E323" s="31" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="324" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A324" s="142"/>
       <c r="B324" s="19" t="s">
-        <v>725</v>
-      </c>
-      <c r="C324" s="183" t="s">
-        <v>737</v>
+        <v>722</v>
+      </c>
+      <c r="C324" s="232" t="s">
+        <v>734</v>
       </c>
       <c r="D324" s="1"/>
-      <c r="E324" s="172" t="s">
-        <v>750</v>
+      <c r="E324" s="208" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="325" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A325" s="142"/>
       <c r="B325" s="69" t="s">
-        <v>726</v>
-      </c>
-      <c r="C325" s="184"/>
+        <v>723</v>
+      </c>
+      <c r="C325" s="233"/>
       <c r="D325" s="69" t="s">
-        <v>740</v>
-      </c>
-      <c r="E325" s="173"/>
+        <v>737</v>
+      </c>
+      <c r="E325" s="228"/>
     </row>
     <row r="326" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A326" s="142"/>
       <c r="B326" s="69" t="s">
-        <v>727</v>
-      </c>
-      <c r="C326" s="184"/>
+        <v>724</v>
+      </c>
+      <c r="C326" s="233"/>
       <c r="D326" s="69" t="s">
-        <v>741</v>
-      </c>
-      <c r="E326" s="173"/>
+        <v>738</v>
+      </c>
+      <c r="E326" s="228"/>
     </row>
     <row r="327" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A327" s="142"/>
       <c r="B327" s="69" t="s">
-        <v>728</v>
-      </c>
-      <c r="C327" s="184"/>
+        <v>725</v>
+      </c>
+      <c r="C327" s="233"/>
       <c r="D327" s="70" t="s">
-        <v>742</v>
-      </c>
-      <c r="E327" s="173"/>
+        <v>739</v>
+      </c>
+      <c r="E327" s="228"/>
     </row>
     <row r="328" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A328" s="142"/>
       <c r="B328" s="69" t="s">
-        <v>729</v>
-      </c>
-      <c r="C328" s="184"/>
+        <v>726</v>
+      </c>
+      <c r="C328" s="233"/>
       <c r="D328" s="1"/>
-      <c r="E328" s="173"/>
+      <c r="E328" s="228"/>
     </row>
     <row r="329" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A329" s="142"/>
       <c r="B329" s="69" t="s">
-        <v>726</v>
-      </c>
-      <c r="C329" s="184"/>
+        <v>723</v>
+      </c>
+      <c r="C329" s="233"/>
       <c r="D329" s="70" t="s">
-        <v>743</v>
-      </c>
-      <c r="E329" s="173"/>
+        <v>740</v>
+      </c>
+      <c r="E329" s="228"/>
     </row>
     <row r="330" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A330" s="142"/>
       <c r="B330" s="69" t="s">
-        <v>727</v>
-      </c>
-      <c r="C330" s="184"/>
+        <v>724</v>
+      </c>
+      <c r="C330" s="233"/>
       <c r="D330" s="71" t="s">
-        <v>744</v>
-      </c>
-      <c r="E330" s="173"/>
+        <v>741</v>
+      </c>
+      <c r="E330" s="228"/>
     </row>
     <row r="331" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A331" s="142"/>
       <c r="B331" s="72" t="s">
-        <v>728</v>
-      </c>
-      <c r="C331" s="184"/>
+        <v>725</v>
+      </c>
+      <c r="C331" s="233"/>
       <c r="D331" s="73" t="s">
-        <v>745</v>
-      </c>
-      <c r="E331" s="173"/>
+        <v>742</v>
+      </c>
+      <c r="E331" s="228"/>
     </row>
     <row r="332" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A332" s="142"/>
       <c r="B332" s="74" t="s">
-        <v>730</v>
-      </c>
-      <c r="C332" s="184"/>
+        <v>727</v>
+      </c>
+      <c r="C332" s="233"/>
       <c r="D332" s="7"/>
-      <c r="E332" s="173"/>
+      <c r="E332" s="228"/>
     </row>
     <row r="333" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A333" s="142"/>
       <c r="B333" s="75" t="s">
-        <v>731</v>
-      </c>
-      <c r="C333" s="184"/>
+        <v>728</v>
+      </c>
+      <c r="C333" s="233"/>
       <c r="D333" s="76" t="s">
-        <v>743</v>
-      </c>
-      <c r="E333" s="173"/>
+        <v>740</v>
+      </c>
+      <c r="E333" s="228"/>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" s="142"/>
       <c r="B334" s="77" t="s">
-        <v>732</v>
-      </c>
-      <c r="C334" s="184"/>
+        <v>729</v>
+      </c>
+      <c r="C334" s="233"/>
       <c r="D334" s="78" t="s">
-        <v>744</v>
-      </c>
-      <c r="E334" s="173"/>
+        <v>741</v>
+      </c>
+      <c r="E334" s="228"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" s="143"/>
       <c r="B335" s="79" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C335" s="80"/>
       <c r="D335" s="81" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E335" s="7"/>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A336" s="185"/>
+      <c r="A336" s="179"/>
       <c r="B336" s="82" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C336" s="59" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D336" s="8"/>
-      <c r="E336" s="173" t="s">
-        <v>751</v>
+      <c r="E336" s="228" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A337" s="185"/>
+      <c r="A337" s="179"/>
       <c r="B337" s="83" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C337" s="1"/>
       <c r="D337" s="31" t="s">
-        <v>746</v>
-      </c>
-      <c r="E337" s="173"/>
+        <v>743</v>
+      </c>
+      <c r="E337" s="228"/>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A338" s="185"/>
+      <c r="A338" s="179"/>
       <c r="B338" s="52" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C338" s="1"/>
       <c r="D338" s="31" t="s">
-        <v>747</v>
-      </c>
-      <c r="E338" s="173"/>
+        <v>744</v>
+      </c>
+      <c r="E338" s="228"/>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A339" s="185"/>
+      <c r="A339" s="179"/>
       <c r="B339" s="52" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C339" s="1"/>
       <c r="D339" s="31" t="s">
-        <v>748</v>
-      </c>
-      <c r="E339" s="173"/>
+        <v>745</v>
+      </c>
+      <c r="E339" s="228"/>
     </row>
     <row r="340" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A340" s="179"/>
+      <c r="A340" s="180"/>
       <c r="B340" s="52" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C340" s="27" t="s">
+        <v>736</v>
+      </c>
+      <c r="D340" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="D340" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="E340" s="174"/>
+      <c r="E340" s="209"/>
     </row>
     <row r="341" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A341" s="178"/>
       <c r="B341" s="4" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C341" s="27" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E341" s="31" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="342" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A342" s="179"/>
+      <c r="A342" s="180"/>
       <c r="B342" s="4" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C342" s="23" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D342" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E342" s="31" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="343" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A343" s="110" t="s">
-        <v>882</v>
-      </c>
-      <c r="B343" s="155" t="s">
-        <v>754</v>
-      </c>
-      <c r="C343" s="156"/>
-      <c r="D343" s="157"/>
+        <v>879</v>
+      </c>
+      <c r="B343" s="201" t="s">
+        <v>751</v>
+      </c>
+      <c r="C343" s="202"/>
+      <c r="D343" s="203"/>
       <c r="E343" s="1"/>
     </row>
     <row r="344" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A344" s="139" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="B344" s="19" t="s">
-        <v>755</v>
-      </c>
-      <c r="C344" s="169" t="s">
-        <v>761</v>
+        <v>752</v>
+      </c>
+      <c r="C344" s="240" t="s">
+        <v>758</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E344" s="172" t="s">
-        <v>767</v>
+        <v>738</v>
+      </c>
+      <c r="E344" s="208" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="345" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A345" s="128"/>
       <c r="B345" s="19" t="s">
-        <v>756</v>
-      </c>
-      <c r="C345" s="170"/>
+        <v>753</v>
+      </c>
+      <c r="C345" s="241"/>
       <c r="D345" s="1"/>
-      <c r="E345" s="173"/>
+      <c r="E345" s="228"/>
     </row>
     <row r="346" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A346" s="128"/>
       <c r="B346" s="69" t="s">
-        <v>726</v>
-      </c>
-      <c r="C346" s="170"/>
+        <v>723</v>
+      </c>
+      <c r="C346" s="241"/>
       <c r="D346" s="70" t="s">
-        <v>741</v>
-      </c>
-      <c r="E346" s="173"/>
+        <v>738</v>
+      </c>
+      <c r="E346" s="228"/>
     </row>
     <row r="347" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A347" s="128"/>
       <c r="B347" s="69" t="s">
-        <v>727</v>
-      </c>
-      <c r="C347" s="170"/>
+        <v>724</v>
+      </c>
+      <c r="C347" s="241"/>
       <c r="D347" s="70" t="s">
-        <v>742</v>
-      </c>
-      <c r="E347" s="173"/>
+        <v>739</v>
+      </c>
+      <c r="E347" s="228"/>
     </row>
     <row r="348" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A348" s="128"/>
       <c r="B348" s="69" t="s">
-        <v>728</v>
-      </c>
-      <c r="C348" s="171"/>
+        <v>725</v>
+      </c>
+      <c r="C348" s="242"/>
       <c r="D348" s="70" t="s">
-        <v>763</v>
-      </c>
-      <c r="E348" s="174"/>
+        <v>760</v>
+      </c>
+      <c r="E348" s="209"/>
     </row>
     <row r="349" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A349" s="128"/>
       <c r="B349" s="84" t="s">
-        <v>757</v>
-      </c>
-      <c r="C349" s="169" t="s">
-        <v>762</v>
-      </c>
-      <c r="D349" s="172" t="s">
-        <v>764</v>
-      </c>
-      <c r="E349" s="164" t="s">
-        <v>768</v>
+        <v>754</v>
+      </c>
+      <c r="C349" s="240" t="s">
+        <v>759</v>
+      </c>
+      <c r="D349" s="208" t="s">
+        <v>761</v>
+      </c>
+      <c r="E349" s="235" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="350" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A350" s="130"/>
       <c r="B350" s="84" t="s">
-        <v>758</v>
-      </c>
-      <c r="C350" s="171"/>
-      <c r="D350" s="174"/>
-      <c r="E350" s="166"/>
+        <v>755</v>
+      </c>
+      <c r="C350" s="242"/>
+      <c r="D350" s="209"/>
+      <c r="E350" s="236"/>
     </row>
     <row r="351" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A351" s="150"/>
+      <c r="A351" s="157"/>
       <c r="B351" s="85" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C351" s="1"/>
       <c r="D351" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E351" s="31" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A352" s="151"/>
+      <c r="A352" s="158"/>
       <c r="B352" s="23" t="s">
-        <v>770</v>
-      </c>
-      <c r="C352" s="175" t="s">
-        <v>774</v>
+        <v>767</v>
+      </c>
+      <c r="C352" s="243" t="s">
+        <v>771</v>
       </c>
       <c r="D352" s="1"/>
-      <c r="E352" s="164" t="s">
-        <v>784</v>
+      <c r="E352" s="235" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A353" s="151"/>
+      <c r="A353" s="158"/>
       <c r="B353" s="69" t="s">
-        <v>726</v>
-      </c>
-      <c r="C353" s="176"/>
+        <v>723</v>
+      </c>
+      <c r="C353" s="244"/>
       <c r="D353" s="86" t="s">
-        <v>741</v>
-      </c>
-      <c r="E353" s="165"/>
+        <v>738</v>
+      </c>
+      <c r="E353" s="246"/>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A354" s="151"/>
+      <c r="A354" s="158"/>
       <c r="B354" s="69" t="s">
-        <v>727</v>
-      </c>
-      <c r="C354" s="176"/>
+        <v>724</v>
+      </c>
+      <c r="C354" s="244"/>
       <c r="D354" s="71" t="s">
-        <v>742</v>
-      </c>
-      <c r="E354" s="165"/>
+        <v>739</v>
+      </c>
+      <c r="E354" s="246"/>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A355" s="151"/>
+      <c r="A355" s="158"/>
       <c r="B355" s="69" t="s">
-        <v>728</v>
-      </c>
-      <c r="C355" s="177"/>
+        <v>725</v>
+      </c>
+      <c r="C355" s="245"/>
       <c r="D355" s="70" t="s">
-        <v>763</v>
-      </c>
-      <c r="E355" s="166"/>
+        <v>760</v>
+      </c>
+      <c r="E355" s="236"/>
     </row>
     <row r="356" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A356" s="151"/>
+      <c r="A356" s="158"/>
       <c r="B356" s="23" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C356" s="23" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D356" s="45" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E356" s="64" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="357" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A357" s="151"/>
+      <c r="A357" s="158"/>
       <c r="B357" s="87" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C357" s="88" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D357" s="89" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E357" s="90"/>
     </row>
     <row r="358" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A358" s="144"/>
       <c r="B358" s="91" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C358" s="92" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D358" s="93" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E358" s="94" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="359" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A359" s="136"/>
       <c r="B359" s="95" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C359" s="96" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="D359" s="46" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E359" s="65" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="360" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A360" s="178"/>
       <c r="B360" s="4" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C360" s="27" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E360" s="31" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="361" spans="1:5" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A361" s="179"/>
+      <c r="A361" s="180"/>
       <c r="B361" s="4" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C361" s="27" t="s">
+        <v>792</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="E361" s="31" t="s">
         <v>795</v>
-      </c>
-      <c r="D361" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="E361" s="31" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="362" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A362" s="127" t="s">
+        <v>785</v>
+      </c>
+      <c r="B362" s="181" t="s">
         <v>788</v>
       </c>
-      <c r="B362" s="147" t="s">
-        <v>791</v>
-      </c>
-      <c r="C362" s="148"/>
-      <c r="D362" s="149"/>
+      <c r="C362" s="182"/>
+      <c r="D362" s="183"/>
       <c r="E362" s="1"/>
     </row>
     <row r="363" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A363" s="128" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C363" s="1"/>
       <c r="D363" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E363" s="26" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="364" spans="1:5" ht="128.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A364" s="130"/>
       <c r="B364" s="4" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C364" s="1"/>
       <c r="D364" s="3" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="E364" s="31" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="365" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A365" s="113"/>
       <c r="B365" s="23" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C365" s="1"/>
       <c r="D365" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E365" s="26" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A366" s="145" t="s">
-        <v>801</v>
-      </c>
-      <c r="B366" s="147" t="s">
-        <v>803</v>
-      </c>
-      <c r="C366" s="148"/>
-      <c r="D366" s="149"/>
+        <v>798</v>
+      </c>
+      <c r="B366" s="181" t="s">
+        <v>800</v>
+      </c>
+      <c r="C366" s="182"/>
+      <c r="D366" s="183"/>
       <c r="E366" s="1"/>
     </row>
     <row r="367" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A367" s="132" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B367" s="23" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E367" s="26" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="368" spans="1:5" ht="128.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A368" s="133"/>
       <c r="B368" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="D368" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="C368" s="4" t="s">
-        <v>807</v>
-      </c>
-      <c r="D368" s="3" t="s">
+      <c r="E368" s="26" t="s">
         <v>808</v>
       </c>
-      <c r="E368" s="26" t="s">
-        <v>811</v>
-      </c>
     </row>
     <row r="369" spans="1:5" ht="128.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A369" s="150"/>
+      <c r="A369" s="157"/>
       <c r="B369" s="4" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C369" s="1"/>
       <c r="D369" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="E369" s="26" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A370" s="158"/>
+      <c r="B370" s="24" t="s">
+        <v>810</v>
+      </c>
+      <c r="C370" s="24" t="s">
+        <v>812</v>
+      </c>
+      <c r="D370" s="26" t="s">
+        <v>815</v>
+      </c>
+      <c r="E370" s="216" t="s">
         <v>817</v>
       </c>
-      <c r="E369" s="26" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A370" s="151"/>
-      <c r="B370" s="24" t="s">
+    </row>
+    <row r="371" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A371" s="159"/>
+      <c r="B371" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="C371" s="4" t="s">
         <v>813</v>
       </c>
-      <c r="C370" s="24" t="s">
+      <c r="D371" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="D370" s="26" t="s">
-        <v>818</v>
-      </c>
-      <c r="E370" s="153" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A371" s="152"/>
-      <c r="B371" s="4" t="s">
-        <v>814</v>
-      </c>
-      <c r="C371" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="D371" s="4" t="s">
-        <v>818</v>
-      </c>
-      <c r="E371" s="154"/>
+      <c r="E371" s="217"/>
     </row>
     <row r="372" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A372" s="125" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B372" s="97" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C372" s="31" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D372" s="1"/>
     </row>
     <row r="373" spans="1:5" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A373" s="125" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B373" s="97" t="s">
+        <v>821</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="D373" s="31" t="s">
         <v>824</v>
-      </c>
-      <c r="C373" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="D373" s="31" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="374" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A374" s="127" t="s">
-        <v>828</v>
-      </c>
-      <c r="B374" s="155" t="s">
-        <v>829</v>
-      </c>
-      <c r="C374" s="157"/>
+        <v>825</v>
+      </c>
+      <c r="B374" s="201" t="s">
+        <v>826</v>
+      </c>
+      <c r="C374" s="203"/>
       <c r="D374" s="6"/>
     </row>
     <row r="375" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A375" s="128" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B375" s="57" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C375" s="98" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D375" s="99"/>
     </row>
     <row r="376" spans="1:5" ht="102.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A376" s="130"/>
       <c r="B376" s="100" t="s">
+        <v>828</v>
+      </c>
+      <c r="C376" s="101" t="s">
+        <v>830</v>
+      </c>
+      <c r="D376" s="65" t="s">
         <v>831</v>
       </c>
-      <c r="C376" s="101" t="s">
-        <v>833</v>
-      </c>
-      <c r="D376" s="65" t="s">
+    </row>
+    <row r="377" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="157"/>
+      <c r="B377" s="184" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="377" spans="1:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A377" s="150"/>
-      <c r="B377" s="162" t="s">
+      <c r="C377" s="186"/>
+      <c r="D377" s="44" t="s">
+        <v>844</v>
+      </c>
+      <c r="E377" s="235" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A378" s="158"/>
+      <c r="B378" s="184" t="s">
+        <v>835</v>
+      </c>
+      <c r="C378" s="186"/>
+      <c r="D378" s="44" t="s">
+        <v>844</v>
+      </c>
+      <c r="E378" s="246"/>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A379" s="158"/>
+      <c r="B379" s="184" t="s">
+        <v>836</v>
+      </c>
+      <c r="C379" s="186"/>
+      <c r="D379" s="44" t="s">
+        <v>845</v>
+      </c>
+      <c r="E379" s="246"/>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A380" s="158"/>
+      <c r="B380" s="184" t="s">
         <v>837</v>
       </c>
-      <c r="C377" s="163"/>
-      <c r="D377" s="44" t="s">
+      <c r="C380" s="186"/>
+      <c r="D380" s="44" t="s">
+        <v>846</v>
+      </c>
+      <c r="E380" s="236"/>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A381" s="158"/>
+      <c r="B381" s="249" t="s">
+        <v>838</v>
+      </c>
+      <c r="C381" s="250"/>
+      <c r="D381" s="44" t="s">
         <v>847</v>
       </c>
-      <c r="E377" s="164" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A378" s="151"/>
-      <c r="B378" s="162" t="s">
-        <v>838</v>
-      </c>
-      <c r="C378" s="163"/>
-      <c r="D378" s="44" t="s">
-        <v>847</v>
-      </c>
-      <c r="E378" s="165"/>
-    </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A379" s="151"/>
-      <c r="B379" s="162" t="s">
+      <c r="E381" s="235" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A382" s="159"/>
+      <c r="B382" s="184" t="s">
         <v>839</v>
       </c>
-      <c r="C379" s="163"/>
-      <c r="D379" s="44" t="s">
+      <c r="C382" s="186"/>
+      <c r="D382" s="44" t="s">
         <v>848</v>
       </c>
-      <c r="E379" s="165"/>
-    </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A380" s="151"/>
-      <c r="B380" s="162" t="s">
-        <v>840</v>
-      </c>
-      <c r="C380" s="163"/>
-      <c r="D380" s="44" t="s">
-        <v>849</v>
-      </c>
-      <c r="E380" s="166"/>
-    </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A381" s="151"/>
-      <c r="B381" s="167" t="s">
-        <v>841</v>
-      </c>
-      <c r="C381" s="168"/>
-      <c r="D381" s="44" t="s">
-        <v>850</v>
-      </c>
-      <c r="E381" s="164" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A382" s="152"/>
-      <c r="B382" s="162" t="s">
-        <v>842</v>
-      </c>
-      <c r="C382" s="163"/>
-      <c r="D382" s="44" t="s">
-        <v>851</v>
-      </c>
-      <c r="E382" s="166"/>
+      <c r="E382" s="236"/>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A383" s="125" t="s">
-        <v>835</v>
-      </c>
-      <c r="B383" s="155" t="s">
+        <v>832</v>
+      </c>
+      <c r="B383" s="201" t="s">
+        <v>840</v>
+      </c>
+      <c r="C383" s="202"/>
+      <c r="D383" s="203"/>
+      <c r="E383" s="1"/>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A384" s="220" t="s">
+        <v>833</v>
+      </c>
+      <c r="B384" s="201" t="s">
+        <v>841</v>
+      </c>
+      <c r="C384" s="202"/>
+      <c r="D384" s="203"/>
+      <c r="E384" s="1"/>
+    </row>
+    <row r="385" spans="1:5" ht="166.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="221"/>
+      <c r="B385" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="C385" s="20" t="s">
         <v>843</v>
       </c>
-      <c r="C383" s="156"/>
-      <c r="D383" s="157"/>
-      <c r="E383" s="1"/>
-    </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A384" s="158" t="s">
-        <v>836</v>
-      </c>
-      <c r="B384" s="155" t="s">
-        <v>844</v>
-      </c>
-      <c r="C384" s="156"/>
-      <c r="D384" s="157"/>
-      <c r="E384" s="1"/>
-    </row>
-    <row r="385" spans="1:5" ht="166.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A385" s="159"/>
-      <c r="B385" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="C385" s="20" t="s">
-        <v>846</v>
-      </c>
       <c r="D385" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="E385" s="3" t="s">
         <v>852</v>
-      </c>
-      <c r="E385" s="3" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="386" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A386" s="120"/>
       <c r="B386" s="1"/>
       <c r="C386" s="13" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D386" s="42"/>
       <c r="E386" s="36"/>
@@ -18125,23 +18112,23 @@
     <row r="387" spans="1:5" ht="273.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A387" s="120"/>
       <c r="B387" s="15" t="s">
+        <v>853</v>
+      </c>
+      <c r="C387" s="37" t="s">
+        <v>855</v>
+      </c>
+      <c r="D387" s="35" t="s">
         <v>856</v>
       </c>
-      <c r="C387" s="37" t="s">
-        <v>858</v>
-      </c>
-      <c r="D387" s="35" t="s">
-        <v>859</v>
-      </c>
       <c r="E387" s="14" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="388" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A388" s="120"/>
       <c r="B388" s="1"/>
       <c r="C388" s="9" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D388" s="1"/>
       <c r="E388" s="1"/>
@@ -18149,191 +18136,50 @@
     <row r="389" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A389" s="120"/>
       <c r="B389" s="17" t="s">
+        <v>859</v>
+      </c>
+      <c r="C389" s="37" t="s">
+        <v>860</v>
+      </c>
+      <c r="D389" s="102" t="s">
+        <v>861</v>
+      </c>
+      <c r="E389" s="28" t="s">
         <v>862</v>
-      </c>
-      <c r="C389" s="37" t="s">
-        <v>863</v>
-      </c>
-      <c r="D389" s="102" t="s">
-        <v>864</v>
-      </c>
-      <c r="E389" s="28" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="390" spans="1:5" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A390" s="113"/>
       <c r="B390" s="15" t="s">
+        <v>864</v>
+      </c>
+      <c r="C390" s="13" t="s">
+        <v>866</v>
+      </c>
+      <c r="D390" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="E390" s="14" t="s">
         <v>867</v>
-      </c>
-      <c r="C390" s="13" t="s">
-        <v>869</v>
-      </c>
-      <c r="D390" s="35" t="s">
-        <v>859</v>
-      </c>
-      <c r="E390" s="14" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="391" spans="1:5" ht="136.5" x14ac:dyDescent="0.2">
       <c r="A391" s="119" t="s">
-        <v>866</v>
-      </c>
-      <c r="B391" s="160" t="s">
-        <v>868</v>
-      </c>
-      <c r="C391" s="161"/>
+        <v>863</v>
+      </c>
+      <c r="B391" s="247" t="s">
+        <v>865</v>
+      </c>
+      <c r="C391" s="248"/>
       <c r="D391" s="14" t="s">
         <v>19</v>
       </c>
       <c r="E391" s="103" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="159">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A21:A27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A56:A63"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="A71:A79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A99"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="A104:A111"/>
-    <mergeCell ref="B112:D112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="A114:A120"/>
-    <mergeCell ref="B114:D114"/>
-    <mergeCell ref="A121:A125"/>
-    <mergeCell ref="B126:D126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="A131:A134"/>
-    <mergeCell ref="A136:A138"/>
-    <mergeCell ref="B139:D139"/>
-    <mergeCell ref="B140:C140"/>
-    <mergeCell ref="A141:A145"/>
-    <mergeCell ref="B141:D141"/>
-    <mergeCell ref="D144:D145"/>
-    <mergeCell ref="E144:E145"/>
-    <mergeCell ref="B146:D146"/>
-    <mergeCell ref="B147:C147"/>
-    <mergeCell ref="A148:A150"/>
-    <mergeCell ref="B148:D148"/>
-    <mergeCell ref="A151:A153"/>
-    <mergeCell ref="B154:D154"/>
-    <mergeCell ref="B155:C155"/>
-    <mergeCell ref="A156:A161"/>
-    <mergeCell ref="B156:D156"/>
-    <mergeCell ref="B164:D164"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="A166:A168"/>
-    <mergeCell ref="B166:D166"/>
-    <mergeCell ref="A169:A172"/>
-    <mergeCell ref="E171:E172"/>
-    <mergeCell ref="B173:D173"/>
-    <mergeCell ref="B174:C174"/>
-    <mergeCell ref="A175:A179"/>
-    <mergeCell ref="B175:D175"/>
-    <mergeCell ref="A180:A183"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="B186:D186"/>
-    <mergeCell ref="B187:C187"/>
-    <mergeCell ref="A188:A192"/>
-    <mergeCell ref="B188:C188"/>
-    <mergeCell ref="B193:D193"/>
-    <mergeCell ref="B194:C194"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="B195:D195"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="B209:D209"/>
-    <mergeCell ref="B210:C210"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="B211:D211"/>
-    <mergeCell ref="D212:E212"/>
-    <mergeCell ref="A213:A222"/>
-    <mergeCell ref="A223:A226"/>
-    <mergeCell ref="A230:A232"/>
-    <mergeCell ref="D232:E232"/>
-    <mergeCell ref="B234:D234"/>
-    <mergeCell ref="E235:E236"/>
-    <mergeCell ref="E238:E241"/>
-    <mergeCell ref="B243:D243"/>
-    <mergeCell ref="B244:C244"/>
-    <mergeCell ref="B245:D245"/>
-    <mergeCell ref="A250:A258"/>
-    <mergeCell ref="D259:E259"/>
-    <mergeCell ref="D262:E262"/>
-    <mergeCell ref="B267:D267"/>
-    <mergeCell ref="B268:C268"/>
-    <mergeCell ref="A269:A273"/>
-    <mergeCell ref="B269:D269"/>
-    <mergeCell ref="D273:E273"/>
-    <mergeCell ref="B274:D274"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A287:A289"/>
-    <mergeCell ref="A291:A293"/>
-    <mergeCell ref="B294:D294"/>
-    <mergeCell ref="C295:C300"/>
-    <mergeCell ref="E295:E300"/>
-    <mergeCell ref="E303:E304"/>
-    <mergeCell ref="A305:A315"/>
-    <mergeCell ref="E305:E306"/>
-    <mergeCell ref="E307:E308"/>
-    <mergeCell ref="E310:E315"/>
-    <mergeCell ref="A316:A321"/>
-    <mergeCell ref="E316:E319"/>
-    <mergeCell ref="B322:D322"/>
-    <mergeCell ref="C324:C334"/>
-    <mergeCell ref="E324:E334"/>
-    <mergeCell ref="A336:A340"/>
-    <mergeCell ref="E336:E340"/>
-    <mergeCell ref="A341:A342"/>
-    <mergeCell ref="B343:D343"/>
-    <mergeCell ref="C344:C348"/>
-    <mergeCell ref="E344:E348"/>
-    <mergeCell ref="C349:C350"/>
-    <mergeCell ref="D349:D350"/>
-    <mergeCell ref="E349:E350"/>
-    <mergeCell ref="A351:A357"/>
-    <mergeCell ref="C352:C355"/>
-    <mergeCell ref="E352:E355"/>
-    <mergeCell ref="A360:A361"/>
     <mergeCell ref="B362:D362"/>
     <mergeCell ref="B366:D366"/>
     <mergeCell ref="A369:A371"/>
@@ -18352,6 +18198,147 @@
     <mergeCell ref="B381:C381"/>
     <mergeCell ref="E381:E382"/>
     <mergeCell ref="B382:C382"/>
+    <mergeCell ref="C344:C348"/>
+    <mergeCell ref="E344:E348"/>
+    <mergeCell ref="C349:C350"/>
+    <mergeCell ref="D349:D350"/>
+    <mergeCell ref="E349:E350"/>
+    <mergeCell ref="A351:A357"/>
+    <mergeCell ref="C352:C355"/>
+    <mergeCell ref="E352:E355"/>
+    <mergeCell ref="A360:A361"/>
+    <mergeCell ref="A316:A321"/>
+    <mergeCell ref="E316:E319"/>
+    <mergeCell ref="B322:D322"/>
+    <mergeCell ref="C324:C334"/>
+    <mergeCell ref="E324:E334"/>
+    <mergeCell ref="A336:A340"/>
+    <mergeCell ref="E336:E340"/>
+    <mergeCell ref="A341:A342"/>
+    <mergeCell ref="B343:D343"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A287:A289"/>
+    <mergeCell ref="A291:A293"/>
+    <mergeCell ref="B294:D294"/>
+    <mergeCell ref="C295:C300"/>
+    <mergeCell ref="E295:E300"/>
+    <mergeCell ref="E303:E304"/>
+    <mergeCell ref="A305:A315"/>
+    <mergeCell ref="E305:E306"/>
+    <mergeCell ref="E307:E308"/>
+    <mergeCell ref="E310:E315"/>
+    <mergeCell ref="A250:A258"/>
+    <mergeCell ref="D259:E259"/>
+    <mergeCell ref="D262:E262"/>
+    <mergeCell ref="B267:D267"/>
+    <mergeCell ref="B268:C268"/>
+    <mergeCell ref="A269:A273"/>
+    <mergeCell ref="B269:D269"/>
+    <mergeCell ref="D273:E273"/>
+    <mergeCell ref="B274:D274"/>
+    <mergeCell ref="A223:A226"/>
+    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="D232:E232"/>
+    <mergeCell ref="B234:D234"/>
+    <mergeCell ref="E235:E236"/>
+    <mergeCell ref="E238:E241"/>
+    <mergeCell ref="B243:D243"/>
+    <mergeCell ref="B244:C244"/>
+    <mergeCell ref="B245:D245"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="B209:D209"/>
+    <mergeCell ref="B210:C210"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="B211:D211"/>
+    <mergeCell ref="D212:E212"/>
+    <mergeCell ref="A213:A222"/>
+    <mergeCell ref="A180:A183"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="B186:D186"/>
+    <mergeCell ref="B187:C187"/>
+    <mergeCell ref="A188:A192"/>
+    <mergeCell ref="B188:C188"/>
+    <mergeCell ref="B193:D193"/>
+    <mergeCell ref="B194:C194"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="B195:D195"/>
+    <mergeCell ref="B164:D164"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="A166:A168"/>
+    <mergeCell ref="B166:D166"/>
+    <mergeCell ref="A169:A172"/>
+    <mergeCell ref="E171:E172"/>
+    <mergeCell ref="B173:D173"/>
+    <mergeCell ref="B174:C174"/>
+    <mergeCell ref="A175:A179"/>
+    <mergeCell ref="B175:D175"/>
+    <mergeCell ref="E144:E145"/>
+    <mergeCell ref="B146:D146"/>
+    <mergeCell ref="B147:C147"/>
+    <mergeCell ref="A148:A150"/>
+    <mergeCell ref="B148:D148"/>
+    <mergeCell ref="A151:A153"/>
+    <mergeCell ref="B154:D154"/>
+    <mergeCell ref="B155:C155"/>
+    <mergeCell ref="A156:A161"/>
+    <mergeCell ref="B156:D156"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="A131:A134"/>
+    <mergeCell ref="A136:A138"/>
+    <mergeCell ref="B139:D139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="A141:A145"/>
+    <mergeCell ref="B141:D141"/>
+    <mergeCell ref="D144:D145"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="A104:A111"/>
+    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="A114:A120"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="A121:A125"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="A71:A79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A99"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A56:A63"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="B17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
